--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128760356</v>
+        <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>86729</v>
+        <v>92768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699154</v>
+        <v>699213</v>
       </c>
       <c r="R9" t="n">
-        <v>6671383</v>
+        <v>6671287</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128760340</v>
+        <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>92768</v>
+        <v>86729</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699213</v>
+        <v>699154</v>
       </c>
       <c r="R10" t="n">
-        <v>6671287</v>
+        <v>6671383</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92752</v>
+        <v>92753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>90990</v>
+        <v>90991</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>90963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92783</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92753</v>
+        <v>92780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>90991</v>
+        <v>91018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>90963</v>
+        <v>90990</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92780</v>
+        <v>92785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91018</v>
+        <v>91023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>90990</v>
+        <v>90995</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,6 +2706,98 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128883852</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>699201</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6671236</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92785</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91023</v>
+        <v>91028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>90995</v>
+        <v>91000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91905</v>
+        <v>91910</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91028</v>
+        <v>91032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>91000</v>
+        <v>91004</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91910</v>
+        <v>91914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91032</v>
+        <v>91037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>91004</v>
+        <v>91009</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91914</v>
+        <v>91919</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>92800</v>
+        <v>86975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R31" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B32" t="n">
-        <v>86975</v>
+        <v>92800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R32" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4606,36 +4606,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129070230</v>
+        <v>129068864</v>
       </c>
       <c r="B41" t="n">
-        <v>86952</v>
+        <v>91016</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249228</v>
+        <v>5734</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4644,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699079</v>
+        <v>699060</v>
       </c>
       <c r="R41" t="n">
-        <v>6671615</v>
+        <v>6671608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4680,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4711,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129068864</v>
+        <v>129068846</v>
       </c>
       <c r="B42" t="n">
-        <v>91016</v>
+        <v>86825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4722,29 +4731,25 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5734</v>
+        <v>427</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4753,10 +4758,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699060</v>
+        <v>699044</v>
       </c>
       <c r="R42" t="n">
-        <v>6671608</v>
+        <v>6671620</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4825,32 +4825,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129068846</v>
+        <v>129070230</v>
       </c>
       <c r="B43" t="n">
-        <v>86825</v>
+        <v>86952</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>427</v>
+        <v>249228</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699044</v>
+        <v>699079</v>
       </c>
       <c r="R43" t="n">
-        <v>6671620</v>
+        <v>6671615</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92837</v>
+        <v>92842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101744</v>
+        <v>101749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91044</v>
+        <v>91047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>87004</v>
+        <v>87007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100745</v>
+        <v>100750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>91016</v>
+        <v>91019</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91927</v>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>129068693</v>
       </c>
       <c r="B24" t="n">
-        <v>86867</v>
+        <v>86870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,37 +2906,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B25" t="n">
-        <v>86867</v>
+        <v>43982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2944,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R25" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2980,6 +2982,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3011,39 +3018,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B26" t="n">
-        <v>43982</v>
+        <v>86870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R26" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3087,11 +3092,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3126,7 +3126,7 @@
         <v>129067850</v>
       </c>
       <c r="B27" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B28" t="n">
-        <v>86876</v>
+        <v>92805</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R28" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>87004</v>
+        <v>86879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R29" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3438,32 +3438,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129064614</v>
+        <v>129068961</v>
       </c>
       <c r="B30" t="n">
-        <v>92800</v>
+        <v>87007</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699036</v>
+        <v>699078</v>
       </c>
       <c r="R30" t="n">
-        <v>6671536</v>
+        <v>6671632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
         <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>129066734</v>
       </c>
       <c r="B32" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129066928</v>
       </c>
       <c r="B33" t="n">
-        <v>91056</v>
+        <v>91059</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>129068763</v>
       </c>
       <c r="B34" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>129067444</v>
       </c>
       <c r="B35" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129069770</v>
+        <v>129070093</v>
       </c>
       <c r="B36" t="n">
-        <v>90284</v>
+        <v>92280</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1595</v>
+        <v>232138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699009</v>
+        <v>699021</v>
       </c>
       <c r="R36" t="n">
-        <v>6671637</v>
+        <v>6671642</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,32 +4186,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129070093</v>
+        <v>129069770</v>
       </c>
       <c r="B37" t="n">
-        <v>92275</v>
+        <v>90287</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>232138</v>
+        <v>1595</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699021</v>
+        <v>699009</v>
       </c>
       <c r="R37" t="n">
-        <v>6671642</v>
+        <v>6671637</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
         <v>129068964</v>
       </c>
       <c r="B38" t="n">
-        <v>87004</v>
+        <v>87007</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>129070090</v>
       </c>
       <c r="B39" t="n">
-        <v>92275</v>
+        <v>92280</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129067907</v>
       </c>
       <c r="B40" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>129068864</v>
       </c>
       <c r="B41" t="n">
-        <v>91016</v>
+        <v>91019</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>129068846</v>
       </c>
       <c r="B42" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>129070230</v>
       </c>
       <c r="B43" t="n">
-        <v>86952</v>
+        <v>86955</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>129066516</v>
       </c>
       <c r="B44" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>129068822</v>
       </c>
       <c r="B45" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068561</v>
       </c>
       <c r="B46" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92812</v>
+        <v>92815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101749</v>
+        <v>101752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91047</v>
+        <v>91050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>87007</v>
+        <v>87010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100750</v>
+        <v>100753</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>91019</v>
+        <v>91022</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91930</v>
+        <v>91933</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>129068693</v>
       </c>
       <c r="B24" t="n">
-        <v>86870</v>
+        <v>86873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,39 +2906,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B25" t="n">
-        <v>43982</v>
+        <v>86873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2946,10 +2944,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R25" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2982,11 +2980,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3018,37 +3011,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B26" t="n">
-        <v>86870</v>
+        <v>43982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3056,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R26" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3092,6 +3087,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3126,7 +3126,7 @@
         <v>129067850</v>
       </c>
       <c r="B27" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129064614</v>
+        <v>129067215</v>
       </c>
       <c r="B28" t="n">
-        <v>92805</v>
+        <v>86882</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3611</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699036</v>
+        <v>698984</v>
       </c>
       <c r="R28" t="n">
-        <v>6671536</v>
+        <v>6671633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B29" t="n">
-        <v>86879</v>
+        <v>87010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R29" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3438,32 +3438,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129068961</v>
+        <v>129064614</v>
       </c>
       <c r="B30" t="n">
-        <v>87007</v>
+        <v>92808</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3739</v>
+        <v>150</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699078</v>
+        <v>699036</v>
       </c>
       <c r="R30" t="n">
-        <v>6671632</v>
+        <v>6671536</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
         <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>129066734</v>
       </c>
       <c r="B32" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129066928</v>
       </c>
       <c r="B33" t="n">
-        <v>91059</v>
+        <v>91062</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>129068763</v>
       </c>
       <c r="B34" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>129067444</v>
       </c>
       <c r="B35" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129070093</v>
+        <v>129069770</v>
       </c>
       <c r="B36" t="n">
-        <v>92280</v>
+        <v>90290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>232138</v>
+        <v>1595</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699021</v>
+        <v>699009</v>
       </c>
       <c r="R36" t="n">
-        <v>6671642</v>
+        <v>6671637</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,32 +4186,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129069770</v>
+        <v>129070093</v>
       </c>
       <c r="B37" t="n">
-        <v>90287</v>
+        <v>92283</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1595</v>
+        <v>232138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699009</v>
+        <v>699021</v>
       </c>
       <c r="R37" t="n">
-        <v>6671637</v>
+        <v>6671642</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
         <v>129068964</v>
       </c>
       <c r="B38" t="n">
-        <v>87007</v>
+        <v>87010</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>129070090</v>
       </c>
       <c r="B39" t="n">
-        <v>92280</v>
+        <v>92283</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129067907</v>
       </c>
       <c r="B40" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129068864</v>
+        <v>129068846</v>
       </c>
       <c r="B41" t="n">
-        <v>91019</v>
+        <v>86831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4617,29 +4617,25 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5734</v>
+        <v>427</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4648,10 +4644,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699060</v>
+        <v>699044</v>
       </c>
       <c r="R41" t="n">
-        <v>6671608</v>
+        <v>6671620</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4680,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4720,10 +4711,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129068846</v>
+        <v>129068864</v>
       </c>
       <c r="B42" t="n">
-        <v>86828</v>
+        <v>91022</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,25 +4722,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>427</v>
+        <v>5734</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4758,10 +4753,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699044</v>
+        <v>699060</v>
       </c>
       <c r="R42" t="n">
-        <v>6671620</v>
+        <v>6671608</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,6 +4789,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4828,7 +4828,7 @@
         <v>129070230</v>
       </c>
       <c r="B43" t="n">
-        <v>86955</v>
+        <v>86958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4930,32 +4930,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B44" t="n">
-        <v>92805</v>
+        <v>86981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R44" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,32 +5035,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129068822</v>
+        <v>129066516</v>
       </c>
       <c r="B45" t="n">
-        <v>86978</v>
+        <v>92808</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699119</v>
+        <v>698988</v>
       </c>
       <c r="R45" t="n">
-        <v>6671545</v>
+        <v>6671638</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5143,7 +5143,7 @@
         <v>129068561</v>
       </c>
       <c r="B46" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>86882</v>
+        <v>87010</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R28" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>87010</v>
+        <v>86882</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R29" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4930,32 +4930,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129068822</v>
+        <v>129066516</v>
       </c>
       <c r="B44" t="n">
-        <v>86981</v>
+        <v>92808</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699119</v>
+        <v>698988</v>
       </c>
       <c r="R44" t="n">
-        <v>6671545</v>
+        <v>6671638</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,32 +5035,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B45" t="n">
-        <v>92808</v>
+        <v>86981</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R45" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2906,37 +2906,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B25" t="n">
-        <v>86873</v>
+        <v>43982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2944,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R25" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2980,6 +2982,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3011,39 +3018,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B26" t="n">
-        <v>43982</v>
+        <v>86873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R26" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3087,11 +3092,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3228,32 +3228,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129068961</v>
+        <v>129064614</v>
       </c>
       <c r="B28" t="n">
-        <v>87010</v>
+        <v>92808</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3739</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699078</v>
+        <v>699036</v>
       </c>
       <c r="R28" t="n">
-        <v>6671632</v>
+        <v>6671536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,32 +3438,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129064614</v>
+        <v>129068961</v>
       </c>
       <c r="B30" t="n">
-        <v>92808</v>
+        <v>87010</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699036</v>
+        <v>699078</v>
       </c>
       <c r="R30" t="n">
-        <v>6671536</v>
+        <v>6671632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B31" t="n">
-        <v>86981</v>
+        <v>92808</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R31" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B32" t="n">
-        <v>92808</v>
+        <v>86981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R32" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92845</v>
+        <v>92852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91050</v>
+        <v>91054</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>91022</v>
+        <v>91026</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91933</v>
+        <v>91940</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>129068693</v>
       </c>
       <c r="B24" t="n">
-        <v>86873</v>
+        <v>86877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,39 +2906,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B25" t="n">
-        <v>43982</v>
+        <v>86877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2946,10 +2944,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R25" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2982,11 +2980,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3018,37 +3011,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B26" t="n">
-        <v>86873</v>
+        <v>43982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3056,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R26" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3092,6 +3087,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3126,7 +3126,7 @@
         <v>129067850</v>
       </c>
       <c r="B27" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129064614</v>
       </c>
       <c r="B28" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B29" t="n">
-        <v>86882</v>
+        <v>87014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R29" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B30" t="n">
-        <v>87010</v>
+        <v>86886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R30" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>92808</v>
+        <v>86985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R31" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B32" t="n">
-        <v>86981</v>
+        <v>92815</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R32" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3756,7 +3756,7 @@
         <v>129066928</v>
       </c>
       <c r="B33" t="n">
-        <v>91062</v>
+        <v>91066</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>129068763</v>
       </c>
       <c r="B34" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>129067444</v>
       </c>
       <c r="B35" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129069770</v>
+        <v>129070093</v>
       </c>
       <c r="B36" t="n">
-        <v>90290</v>
+        <v>92290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1595</v>
+        <v>232138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699009</v>
+        <v>699021</v>
       </c>
       <c r="R36" t="n">
-        <v>6671637</v>
+        <v>6671642</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,32 +4186,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129070093</v>
+        <v>129069770</v>
       </c>
       <c r="B37" t="n">
-        <v>92283</v>
+        <v>90294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>232138</v>
+        <v>1595</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699021</v>
+        <v>699009</v>
       </c>
       <c r="R37" t="n">
-        <v>6671642</v>
+        <v>6671637</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
         <v>129068964</v>
       </c>
       <c r="B38" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>129070090</v>
       </c>
       <c r="B39" t="n">
-        <v>92283</v>
+        <v>92290</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129067907</v>
       </c>
       <c r="B40" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>129068846</v>
       </c>
       <c r="B41" t="n">
-        <v>86831</v>
+        <v>86835</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>129068864</v>
       </c>
       <c r="B42" t="n">
-        <v>91022</v>
+        <v>91026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>129070230</v>
       </c>
       <c r="B43" t="n">
-        <v>86958</v>
+        <v>86962</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>129066516</v>
       </c>
       <c r="B44" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>129068822</v>
       </c>
       <c r="B45" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068561</v>
       </c>
       <c r="B46" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -4606,10 +4606,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129068846</v>
+        <v>129068864</v>
       </c>
       <c r="B41" t="n">
-        <v>86835</v>
+        <v>91026</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4617,25 +4617,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>427</v>
+        <v>5734</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4644,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699044</v>
+        <v>699060</v>
       </c>
       <c r="R41" t="n">
-        <v>6671620</v>
+        <v>6671608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4680,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4711,40 +4720,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129068864</v>
+        <v>129070230</v>
       </c>
       <c r="B42" t="n">
-        <v>91026</v>
+        <v>86962</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5734</v>
+        <v>249228</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4753,10 +4758,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699060</v>
+        <v>699079</v>
       </c>
       <c r="R42" t="n">
-        <v>6671608</v>
+        <v>6671615</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,11 +4794,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4825,32 +4825,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129070230</v>
+        <v>129068846</v>
       </c>
       <c r="B43" t="n">
-        <v>86962</v>
+        <v>86835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>249228</v>
+        <v>427</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699079</v>
+        <v>699044</v>
       </c>
       <c r="R43" t="n">
-        <v>6671615</v>
+        <v>6671620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91940</v>
+        <v>91947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>129068693</v>
       </c>
       <c r="B24" t="n">
-        <v>86877</v>
+        <v>86884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>129068659</v>
       </c>
       <c r="B25" t="n">
-        <v>86877</v>
+        <v>86884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>129067850</v>
       </c>
       <c r="B27" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129064614</v>
       </c>
       <c r="B28" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>87014</v>
+        <v>86893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R29" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B30" t="n">
-        <v>86886</v>
+        <v>87021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3449,21 +3449,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R30" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B31" t="n">
-        <v>86985</v>
+        <v>92822</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R31" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B32" t="n">
-        <v>92815</v>
+        <v>86992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R32" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,44 +3753,36 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129066928</v>
+        <v>129068763</v>
       </c>
       <c r="B33" t="n">
-        <v>91066</v>
+        <v>86992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -3799,10 +3791,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699058</v>
+        <v>699044</v>
       </c>
       <c r="R33" t="n">
-        <v>6671601</v>
+        <v>6671648</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3835,11 +3827,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3871,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129068763</v>
+        <v>129067444</v>
       </c>
       <c r="B34" t="n">
-        <v>86985</v>
+        <v>86893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3882,21 +3869,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3611</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699044</v>
+        <v>698998</v>
       </c>
       <c r="R34" t="n">
-        <v>6671648</v>
+        <v>6671470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3976,32 +3963,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129067444</v>
+        <v>129069770</v>
       </c>
       <c r="B35" t="n">
-        <v>86886</v>
+        <v>90301</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3611</v>
+        <v>1595</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4014,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>698998</v>
+        <v>699009</v>
       </c>
       <c r="R35" t="n">
-        <v>6671470</v>
+        <v>6671637</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4084,7 +4071,7 @@
         <v>129070093</v>
       </c>
       <c r="B36" t="n">
-        <v>92290</v>
+        <v>92297</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,32 +4173,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129069770</v>
+        <v>129068964</v>
       </c>
       <c r="B37" t="n">
-        <v>90294</v>
+        <v>87021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1595</v>
+        <v>3739</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4224,10 +4211,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699009</v>
+        <v>699076</v>
       </c>
       <c r="R37" t="n">
-        <v>6671637</v>
+        <v>6671622</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,32 +4278,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129068964</v>
+        <v>129070090</v>
       </c>
       <c r="B38" t="n">
-        <v>87014</v>
+        <v>92297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3739</v>
+        <v>232138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4329,10 +4316,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699076</v>
+        <v>698978</v>
       </c>
       <c r="R38" t="n">
-        <v>6671622</v>
+        <v>6671642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,32 +4383,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129070090</v>
+        <v>129067907</v>
       </c>
       <c r="B39" t="n">
-        <v>92290</v>
+        <v>86893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>232138</v>
+        <v>3611</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>698978</v>
+        <v>699076</v>
       </c>
       <c r="R39" t="n">
-        <v>6671642</v>
+        <v>6671622</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4501,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129067907</v>
+        <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>86886</v>
+        <v>86842</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4499,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3611</v>
+        <v>427</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4539,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699076</v>
+        <v>699044</v>
       </c>
       <c r="R40" t="n">
-        <v>6671622</v>
+        <v>6671620</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4606,40 +4593,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129068864</v>
+        <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>91026</v>
+        <v>86969</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5734</v>
+        <v>249228</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4648,10 +4631,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699060</v>
+        <v>699079</v>
       </c>
       <c r="R41" t="n">
-        <v>6671608</v>
+        <v>6671615</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4667,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4720,36 +4698,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129070230</v>
+        <v>129068864</v>
       </c>
       <c r="B42" t="n">
-        <v>86962</v>
+        <v>91033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>249228</v>
+        <v>5734</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4758,10 +4740,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699079</v>
+        <v>699060</v>
       </c>
       <c r="R42" t="n">
-        <v>6671615</v>
+        <v>6671608</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,6 +4776,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4825,32 +4812,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129068846</v>
+        <v>129066516</v>
       </c>
       <c r="B43" t="n">
-        <v>86835</v>
+        <v>92822</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>427</v>
+        <v>150</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4863,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699044</v>
+        <v>698988</v>
       </c>
       <c r="R43" t="n">
-        <v>6671620</v>
+        <v>6671638</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4930,32 +4917,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B44" t="n">
-        <v>92815</v>
+        <v>86992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4955,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R44" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,10 +5022,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129068822</v>
+        <v>129068561</v>
       </c>
       <c r="B45" t="n">
-        <v>86985</v>
+        <v>92825</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5046,21 +5033,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6003295</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5073,10 +5060,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699119</v>
+        <v>698941</v>
       </c>
       <c r="R45" t="n">
-        <v>6671545</v>
+        <v>6671657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5140,36 +5127,44 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129068561</v>
+        <v>129066928</v>
       </c>
       <c r="B46" t="n">
-        <v>92818</v>
+        <v>91073</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>1357</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5178,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>698941</v>
+        <v>699058</v>
       </c>
       <c r="R46" t="n">
-        <v>6671657</v>
+        <v>6671601</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,6 +5209,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128760342</v>
       </c>
       <c r="B2" t="n">
-        <v>92852</v>
+        <v>92861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128760348</v>
       </c>
       <c r="B3" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128760352</v>
       </c>
       <c r="B4" t="n">
-        <v>92471</v>
+        <v>92480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128760344</v>
       </c>
       <c r="B5" t="n">
-        <v>92822</v>
+        <v>92831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128760349</v>
       </c>
       <c r="B6" t="n">
-        <v>91065</v>
+        <v>91074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128760345</v>
       </c>
       <c r="B7" t="n">
-        <v>86786</v>
+        <v>86795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128760358</v>
       </c>
       <c r="B8" t="n">
-        <v>101762</v>
+        <v>101771</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128760340</v>
       </c>
       <c r="B9" t="n">
-        <v>92838</v>
+        <v>92847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128760356</v>
       </c>
       <c r="B10" t="n">
-        <v>86786</v>
+        <v>86795</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128760357</v>
       </c>
       <c r="B11" t="n">
-        <v>98703</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128760350</v>
       </c>
       <c r="B12" t="n">
-        <v>92815</v>
+        <v>92824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128760338</v>
       </c>
       <c r="B13" t="n">
-        <v>92815</v>
+        <v>92824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128760346</v>
       </c>
       <c r="B14" t="n">
-        <v>91054</v>
+        <v>91063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128760354</v>
       </c>
       <c r="B15" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128760341</v>
       </c>
       <c r="B16" t="n">
-        <v>91065</v>
+        <v>91074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128760347</v>
       </c>
       <c r="B17" t="n">
-        <v>87014</v>
+        <v>87023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128760359</v>
       </c>
       <c r="B18" t="n">
-        <v>98703</v>
+        <v>98712</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128760355</v>
       </c>
       <c r="B19" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>128760339</v>
       </c>
       <c r="B20" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>128760353</v>
       </c>
       <c r="B21" t="n">
-        <v>100763</v>
+        <v>100772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>128760351</v>
       </c>
       <c r="B22" t="n">
-        <v>91026</v>
+        <v>91035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>129068693</v>
       </c>
       <c r="B24" t="n">
-        <v>86884</v>
+        <v>86886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>129068659</v>
       </c>
       <c r="B25" t="n">
-        <v>86884</v>
+        <v>86886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>129067850</v>
       </c>
       <c r="B27" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129064614</v>
       </c>
       <c r="B28" t="n">
-        <v>92822</v>
+        <v>92824</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>129068961</v>
       </c>
       <c r="B30" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>92822</v>
+        <v>86994</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R31" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B32" t="n">
-        <v>86992</v>
+        <v>92824</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R32" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3756,7 +3756,7 @@
         <v>129068763</v>
       </c>
       <c r="B33" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129067444</v>
       </c>
       <c r="B34" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>129069770</v>
       </c>
       <c r="B35" t="n">
-        <v>90301</v>
+        <v>90303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129070093</v>
       </c>
       <c r="B36" t="n">
-        <v>92297</v>
+        <v>92299</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129068964</v>
       </c>
       <c r="B37" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129070090</v>
       </c>
       <c r="B38" t="n">
-        <v>92297</v>
+        <v>92299</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>129067907</v>
       </c>
       <c r="B39" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>86842</v>
+        <v>86844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4593,36 +4593,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129070230</v>
+        <v>129068864</v>
       </c>
       <c r="B41" t="n">
-        <v>86969</v>
+        <v>91035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249228</v>
+        <v>5734</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4631,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699079</v>
+        <v>699060</v>
       </c>
       <c r="R41" t="n">
-        <v>6671615</v>
+        <v>6671608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4667,6 +4671,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4698,40 +4707,36 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129068864</v>
+        <v>129070230</v>
       </c>
       <c r="B42" t="n">
-        <v>91033</v>
+        <v>86971</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5734</v>
+        <v>249228</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699060</v>
+        <v>699079</v>
       </c>
       <c r="R42" t="n">
-        <v>6671608</v>
+        <v>6671615</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4776,11 +4781,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4815,7 +4815,7 @@
         <v>129066516</v>
       </c>
       <c r="B43" t="n">
-        <v>92822</v>
+        <v>92824</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>129068822</v>
       </c>
       <c r="B44" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129068561</v>
       </c>
       <c r="B45" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>129066928</v>
       </c>
       <c r="B46" t="n">
-        <v>91073</v>
+        <v>91075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3228,32 +3228,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129064614</v>
+        <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>92824</v>
+        <v>87023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699036</v>
+        <v>699078</v>
       </c>
       <c r="R28" t="n">
-        <v>6671536</v>
+        <v>6671632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,32 +3438,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129068961</v>
+        <v>129064614</v>
       </c>
       <c r="B30" t="n">
-        <v>87023</v>
+        <v>92824</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3739</v>
+        <v>150</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699078</v>
+        <v>699036</v>
       </c>
       <c r="R30" t="n">
-        <v>6671632</v>
+        <v>6671536</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B31" t="n">
-        <v>86994</v>
+        <v>92824</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R31" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B32" t="n">
-        <v>92824</v>
+        <v>86994</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R32" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2801,7 +2801,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129068693</v>
+        <v>129068659</v>
       </c>
       <c r="B24" t="n">
         <v>86886</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698993</v>
+        <v>699037</v>
       </c>
       <c r="R24" t="n">
-        <v>6671484</v>
+        <v>6671604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,37 +2906,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B25" t="n">
-        <v>86886</v>
+        <v>43982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2944,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R25" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2980,6 +2982,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3011,39 +3018,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129069986</v>
+        <v>129067850</v>
       </c>
       <c r="B26" t="n">
-        <v>43982</v>
+        <v>86895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101735</v>
+        <v>3611</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699009</v>
+        <v>699075</v>
       </c>
       <c r="R26" t="n">
-        <v>6671637</v>
+        <v>6671620</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3087,11 +3092,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3123,7 +3123,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129067850</v>
+        <v>129067215</v>
       </c>
       <c r="B27" t="n">
         <v>86895</v>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699075</v>
+        <v>698984</v>
       </c>
       <c r="R27" t="n">
-        <v>6671620</v>
+        <v>6671633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B29" t="n">
-        <v>86895</v>
+        <v>92824</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R29" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129064614</v>
+        <v>129066734</v>
       </c>
       <c r="B30" t="n">
         <v>92824</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699036</v>
+        <v>699028</v>
       </c>
       <c r="R30" t="n">
-        <v>6671536</v>
+        <v>6671663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>92824</v>
+        <v>86994</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R31" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129068748</v>
+        <v>129068763</v>
       </c>
       <c r="B32" t="n">
         <v>86994</v>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698990</v>
+        <v>699044</v>
       </c>
       <c r="R32" t="n">
-        <v>6671640</v>
+        <v>6671648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129068763</v>
+        <v>129067444</v>
       </c>
       <c r="B33" t="n">
-        <v>86994</v>
+        <v>86895</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>3611</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699044</v>
+        <v>698998</v>
       </c>
       <c r="R33" t="n">
-        <v>6671648</v>
+        <v>6671470</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3858,32 +3858,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129067444</v>
+        <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>86895</v>
+        <v>90303</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3611</v>
+        <v>1595</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>698998</v>
+        <v>699009</v>
       </c>
       <c r="R34" t="n">
-        <v>6671470</v>
+        <v>6671637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3963,32 +3963,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129069770</v>
+        <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>90303</v>
+        <v>92299</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1595</v>
+        <v>232138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699009</v>
+        <v>699021</v>
       </c>
       <c r="R35" t="n">
-        <v>6671637</v>
+        <v>6671642</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4068,32 +4068,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129070093</v>
+        <v>129068964</v>
       </c>
       <c r="B36" t="n">
-        <v>92299</v>
+        <v>87023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>232138</v>
+        <v>3739</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699021</v>
+        <v>699076</v>
       </c>
       <c r="R36" t="n">
-        <v>6671642</v>
+        <v>6671622</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129068964</v>
+        <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>87023</v>
+        <v>92299</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3739</v>
+        <v>232138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699076</v>
+        <v>698978</v>
       </c>
       <c r="R37" t="n">
-        <v>6671622</v>
+        <v>6671642</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4278,32 +4278,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129070090</v>
+        <v>129067907</v>
       </c>
       <c r="B38" t="n">
-        <v>92299</v>
+        <v>86895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>232138</v>
+        <v>3611</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>698978</v>
+        <v>699076</v>
       </c>
       <c r="R38" t="n">
-        <v>6671642</v>
+        <v>6671622</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4383,32 +4383,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129067907</v>
+        <v>129070230</v>
       </c>
       <c r="B39" t="n">
-        <v>86895</v>
+        <v>86971</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3611</v>
+        <v>249228</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699076</v>
+        <v>699079</v>
       </c>
       <c r="R39" t="n">
-        <v>6671622</v>
+        <v>6671615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4707,32 +4707,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129070230</v>
+        <v>129068822</v>
       </c>
       <c r="B42" t="n">
-        <v>86971</v>
+        <v>86994</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>249228</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699079</v>
+        <v>699119</v>
       </c>
       <c r="R42" t="n">
-        <v>6671615</v>
+        <v>6671545</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4917,10 +4917,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129068822</v>
+        <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>86994</v>
+        <v>92827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4928,21 +4928,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699119</v>
+        <v>698941</v>
       </c>
       <c r="R44" t="n">
-        <v>6671545</v>
+        <v>6671657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5022,36 +5022,44 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129068561</v>
+        <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>92827</v>
+        <v>91075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>1357</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5060,10 +5068,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>698941</v>
+        <v>699058</v>
       </c>
       <c r="R45" t="n">
-        <v>6671657</v>
+        <v>6671601</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,6 +5104,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5127,10 +5140,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129066928</v>
+        <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>91075</v>
+        <v>86887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5138,33 +5151,25 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1357</v>
+        <v>445</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5173,10 +5178,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699058</v>
+        <v>698993</v>
       </c>
       <c r="R46" t="n">
-        <v>6671601</v>
+        <v>6671484</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5209,11 +5214,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91949</v>
+        <v>91957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>129068659</v>
       </c>
       <c r="B24" t="n">
-        <v>86886</v>
+        <v>86887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>129067850</v>
       </c>
       <c r="B26" t="n">
-        <v>86895</v>
+        <v>86896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,32 +3123,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B27" t="n">
-        <v>86895</v>
+        <v>92810</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R27" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B28" t="n">
-        <v>87023</v>
+        <v>86896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R28" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129064614</v>
+        <v>129068961</v>
       </c>
       <c r="B29" t="n">
-        <v>92824</v>
+        <v>87024</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699036</v>
+        <v>699078</v>
       </c>
       <c r="R29" t="n">
-        <v>6671536</v>
+        <v>6671632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
         <v>129066734</v>
       </c>
       <c r="B30" t="n">
-        <v>92824</v>
+        <v>92810</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>129068763</v>
       </c>
       <c r="B32" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129067444</v>
       </c>
       <c r="B33" t="n">
-        <v>86895</v>
+        <v>86896</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>90303</v>
+        <v>90304</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>92299</v>
+        <v>92313</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129068964</v>
       </c>
       <c r="B36" t="n">
-        <v>87023</v>
+        <v>87024</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>92299</v>
+        <v>92313</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129067907</v>
       </c>
       <c r="B38" t="n">
-        <v>86895</v>
+        <v>86896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129070230</v>
+        <v>129068846</v>
       </c>
       <c r="B39" t="n">
-        <v>86971</v>
+        <v>86845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>249228</v>
+        <v>427</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699079</v>
+        <v>699044</v>
       </c>
       <c r="R39" t="n">
-        <v>6671615</v>
+        <v>6671620</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129068846</v>
+        <v>129068864</v>
       </c>
       <c r="B40" t="n">
-        <v>86844</v>
+        <v>91036</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,25 +4499,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>427</v>
+        <v>5734</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4526,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699044</v>
+        <v>699060</v>
       </c>
       <c r="R40" t="n">
-        <v>6671620</v>
+        <v>6671608</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,6 +4566,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4593,40 +4602,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129068864</v>
+        <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>91035</v>
+        <v>86972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5734</v>
+        <v>249228</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4635,10 +4640,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699060</v>
+        <v>699079</v>
       </c>
       <c r="R41" t="n">
-        <v>6671608</v>
+        <v>6671615</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,11 +4676,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4707,32 +4707,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129068822</v>
+        <v>129066516</v>
       </c>
       <c r="B42" t="n">
-        <v>86994</v>
+        <v>92810</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699119</v>
+        <v>698988</v>
       </c>
       <c r="R42" t="n">
-        <v>6671545</v>
+        <v>6671638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,32 +4812,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B43" t="n">
-        <v>92824</v>
+        <v>86995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R43" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
         <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,32 +3123,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129064614</v>
+        <v>129067215</v>
       </c>
       <c r="B27" t="n">
-        <v>92810</v>
+        <v>86896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>150</v>
+        <v>3611</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699036</v>
+        <v>698984</v>
       </c>
       <c r="R27" t="n">
-        <v>6671536</v>
+        <v>6671633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>86896</v>
+        <v>87024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R28" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129068961</v>
+        <v>129064614</v>
       </c>
       <c r="B29" t="n">
-        <v>87024</v>
+        <v>92811</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3739</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699078</v>
+        <v>699036</v>
       </c>
       <c r="R29" t="n">
-        <v>6671632</v>
+        <v>6671536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3438,32 +3438,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B30" t="n">
-        <v>92810</v>
+        <v>86995</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R30" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B31" t="n">
-        <v>86995</v>
+        <v>92811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R31" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
         <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>92313</v>
+        <v>92314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>92313</v>
+        <v>92314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>129066516</v>
       </c>
       <c r="B42" t="n">
-        <v>92810</v>
+        <v>92811</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3123,32 +3123,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B27" t="n">
-        <v>86896</v>
+        <v>92811</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R27" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129064614</v>
+        <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>92811</v>
+        <v>86896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3611</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699036</v>
+        <v>698984</v>
       </c>
       <c r="R29" t="n">
-        <v>6671536</v>
+        <v>6671633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129068846</v>
+        <v>129068864</v>
       </c>
       <c r="B39" t="n">
-        <v>86845</v>
+        <v>91036</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4394,25 +4394,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>427</v>
+        <v>5734</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4421,10 +4425,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699044</v>
+        <v>699060</v>
       </c>
       <c r="R39" t="n">
-        <v>6671620</v>
+        <v>6671608</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4457,6 +4461,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4488,10 +4497,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129068864</v>
+        <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>91036</v>
+        <v>86845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,29 +4508,25 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5734</v>
+        <v>427</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4530,10 +4535,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699060</v>
+        <v>699044</v>
       </c>
       <c r="R40" t="n">
-        <v>6671608</v>
+        <v>6671620</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4566,11 +4571,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2712,7 +2712,7 @@
         <v>128883852</v>
       </c>
       <c r="B23" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2801,37 +2801,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B24" t="n">
-        <v>86887</v>
+        <v>43982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2839,10 +2841,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R24" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2875,6 +2877,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2906,39 +2913,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B25" t="n">
-        <v>43982</v>
+        <v>86890</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2946,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R25" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2982,11 +2987,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3021,7 +3021,7 @@
         <v>129067850</v>
       </c>
       <c r="B26" t="n">
-        <v>86896</v>
+        <v>86899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>129064614</v>
       </c>
       <c r="B27" t="n">
-        <v>92811</v>
+        <v>92814</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>86896</v>
+        <v>86899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3438,32 +3438,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129068748</v>
+        <v>129066734</v>
       </c>
       <c r="B30" t="n">
-        <v>86995</v>
+        <v>92814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>698990</v>
+        <v>699028</v>
       </c>
       <c r="R30" t="n">
-        <v>6671640</v>
+        <v>6671663</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3543,32 +3543,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129066734</v>
+        <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>92811</v>
+        <v>86998</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699028</v>
+        <v>698990</v>
       </c>
       <c r="R31" t="n">
-        <v>6671663</v>
+        <v>6671640</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3651,7 +3651,7 @@
         <v>129068763</v>
       </c>
       <c r="B32" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129067444</v>
       </c>
       <c r="B33" t="n">
-        <v>86896</v>
+        <v>86899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>90304</v>
+        <v>90307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>92314</v>
+        <v>92317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129068964</v>
       </c>
       <c r="B36" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>92314</v>
+        <v>92317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129067907</v>
       </c>
       <c r="B38" t="n">
-        <v>86896</v>
+        <v>86899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>129068864</v>
       </c>
       <c r="B39" t="n">
-        <v>91036</v>
+        <v>91039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>86845</v>
+        <v>86848</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>86972</v>
+        <v>86975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4707,32 +4707,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B42" t="n">
-        <v>92811</v>
+        <v>86998</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R42" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,32 +4812,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129068822</v>
+        <v>129066516</v>
       </c>
       <c r="B43" t="n">
-        <v>86995</v>
+        <v>92814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699119</v>
+        <v>698988</v>
       </c>
       <c r="R43" t="n">
-        <v>6671545</v>
+        <v>6671638</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
         <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91076</v>
+        <v>91079</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86887</v>
+        <v>86890</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3123,32 +3123,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129064614</v>
+        <v>129068961</v>
       </c>
       <c r="B27" t="n">
-        <v>92814</v>
+        <v>87027</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699036</v>
+        <v>699078</v>
       </c>
       <c r="R27" t="n">
-        <v>6671536</v>
+        <v>6671632</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B28" t="n">
-        <v>87027</v>
+        <v>86899</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R28" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B29" t="n">
-        <v>86899</v>
+        <v>92814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R29" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4707,32 +4707,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129068822</v>
+        <v>129066516</v>
       </c>
       <c r="B42" t="n">
-        <v>86998</v>
+        <v>92814</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699119</v>
+        <v>698988</v>
       </c>
       <c r="R42" t="n">
-        <v>6671545</v>
+        <v>6671638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,32 +4812,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B43" t="n">
-        <v>92814</v>
+        <v>86998</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R43" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2801,39 +2801,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B24" t="n">
-        <v>43982</v>
+        <v>86892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2841,10 +2839,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R24" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2877,11 +2875,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2913,37 +2906,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B25" t="n">
-        <v>86890</v>
+        <v>43982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2951,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R25" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2987,6 +2982,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3021,7 +3021,7 @@
         <v>129067850</v>
       </c>
       <c r="B26" t="n">
-        <v>86899</v>
+        <v>86901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B27" t="n">
-        <v>87027</v>
+        <v>86901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R27" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>86899</v>
+        <v>87029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R28" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3336,7 +3336,7 @@
         <v>129064614</v>
       </c>
       <c r="B29" t="n">
-        <v>92814</v>
+        <v>92816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>129066734</v>
       </c>
       <c r="B30" t="n">
-        <v>92814</v>
+        <v>92816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>129068763</v>
       </c>
       <c r="B32" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129067444</v>
       </c>
       <c r="B33" t="n">
-        <v>86899</v>
+        <v>86901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>90307</v>
+        <v>90309</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>92317</v>
+        <v>92319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129068964</v>
       </c>
       <c r="B36" t="n">
-        <v>87027</v>
+        <v>87029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>92317</v>
+        <v>92319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129067907</v>
       </c>
       <c r="B38" t="n">
-        <v>86899</v>
+        <v>86901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>129068864</v>
       </c>
       <c r="B39" t="n">
-        <v>91039</v>
+        <v>91041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>86848</v>
+        <v>86850</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>86975</v>
+        <v>86977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>129066516</v>
       </c>
       <c r="B42" t="n">
-        <v>92814</v>
+        <v>92816</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>129068822</v>
       </c>
       <c r="B43" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91079</v>
+        <v>91081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86890</v>
+        <v>86892</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2804,7 +2804,7 @@
         <v>129068659</v>
       </c>
       <c r="B24" t="n">
-        <v>86892</v>
+        <v>86896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>129067850</v>
       </c>
       <c r="B26" t="n">
-        <v>86901</v>
+        <v>86905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,32 +3123,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B27" t="n">
-        <v>86901</v>
+        <v>92820</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R27" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
         <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>87029</v>
+        <v>87033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129064614</v>
+        <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>92816</v>
+        <v>86905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3611</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699036</v>
+        <v>698984</v>
       </c>
       <c r="R29" t="n">
-        <v>6671536</v>
+        <v>6671633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
         <v>129066734</v>
       </c>
       <c r="B30" t="n">
-        <v>92816</v>
+        <v>92820</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>129068763</v>
       </c>
       <c r="B32" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129067444</v>
       </c>
       <c r="B33" t="n">
-        <v>86901</v>
+        <v>86905</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>90309</v>
+        <v>90313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>92319</v>
+        <v>92323</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129068964</v>
       </c>
       <c r="B36" t="n">
-        <v>87029</v>
+        <v>87033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>92319</v>
+        <v>92323</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129067907</v>
       </c>
       <c r="B38" t="n">
-        <v>86901</v>
+        <v>86905</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>129068864</v>
       </c>
       <c r="B39" t="n">
-        <v>91041</v>
+        <v>91045</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>86850</v>
+        <v>86854</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>86977</v>
+        <v>86981</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>129066516</v>
       </c>
       <c r="B42" t="n">
-        <v>92816</v>
+        <v>92820</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>129068822</v>
       </c>
       <c r="B43" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91081</v>
+        <v>91085</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86892</v>
+        <v>86896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2804,7 +2804,7 @@
         <v>129068659</v>
       </c>
       <c r="B24" t="n">
-        <v>86896</v>
+        <v>86897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>129067850</v>
       </c>
       <c r="B26" t="n">
-        <v>86905</v>
+        <v>86906</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>129064614</v>
       </c>
       <c r="B27" t="n">
-        <v>92820</v>
+        <v>92821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B28" t="n">
-        <v>87033</v>
+        <v>86906</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R28" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B29" t="n">
-        <v>86905</v>
+        <v>87034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R29" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
         <v>129066734</v>
       </c>
       <c r="B30" t="n">
-        <v>92820</v>
+        <v>92821</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>129068748</v>
       </c>
       <c r="B31" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>129068763</v>
       </c>
       <c r="B32" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>129067444</v>
       </c>
       <c r="B33" t="n">
-        <v>86905</v>
+        <v>86906</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>90313</v>
+        <v>90314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129068964</v>
       </c>
       <c r="B36" t="n">
-        <v>87033</v>
+        <v>87034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>129067907</v>
       </c>
       <c r="B38" t="n">
-        <v>86905</v>
+        <v>86906</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129068864</v>
+        <v>129068846</v>
       </c>
       <c r="B39" t="n">
-        <v>91045</v>
+        <v>86855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4394,29 +4394,25 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5734</v>
+        <v>427</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4425,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699060</v>
+        <v>699044</v>
       </c>
       <c r="R39" t="n">
-        <v>6671608</v>
+        <v>6671620</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,11 +4457,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4497,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129068846</v>
+        <v>129068864</v>
       </c>
       <c r="B40" t="n">
-        <v>86854</v>
+        <v>91046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4508,25 +4499,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>427</v>
+        <v>5734</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4535,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699044</v>
+        <v>699060</v>
       </c>
       <c r="R40" t="n">
-        <v>6671620</v>
+        <v>6671608</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4571,6 +4566,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4605,7 +4605,7 @@
         <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>86981</v>
+        <v>86982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>129066516</v>
       </c>
       <c r="B42" t="n">
-        <v>92820</v>
+        <v>92821</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>129068822</v>
       </c>
       <c r="B43" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>92823</v>
+        <v>92824</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91085</v>
+        <v>91086</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86896</v>
+        <v>86897</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3123,32 +3123,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129064614</v>
+        <v>129067215</v>
       </c>
       <c r="B27" t="n">
-        <v>92821</v>
+        <v>86906</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>150</v>
+        <v>3611</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699036</v>
+        <v>698984</v>
       </c>
       <c r="R27" t="n">
-        <v>6671536</v>
+        <v>6671633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,32 +3228,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B28" t="n">
-        <v>86906</v>
+        <v>92821</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R28" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2801,37 +2801,39 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B24" t="n">
-        <v>86897</v>
+        <v>43982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2839,10 +2841,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R24" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2875,6 +2877,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2906,39 +2913,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B25" t="n">
-        <v>43982</v>
+        <v>86897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2946,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R25" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2982,11 +2987,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4383,32 +4383,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129068846</v>
+        <v>129070230</v>
       </c>
       <c r="B39" t="n">
-        <v>86855</v>
+        <v>86982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>427</v>
+        <v>249228</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699044</v>
+        <v>699079</v>
       </c>
       <c r="R39" t="n">
-        <v>6671620</v>
+        <v>6671615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129068864</v>
+        <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>91046</v>
+        <v>86855</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,29 +4499,25 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5734</v>
+        <v>427</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4530,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699060</v>
+        <v>699044</v>
       </c>
       <c r="R40" t="n">
-        <v>6671608</v>
+        <v>6671620</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4566,11 +4562,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4602,36 +4593,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129070230</v>
+        <v>129068864</v>
       </c>
       <c r="B41" t="n">
-        <v>86982</v>
+        <v>91046</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249228</v>
+        <v>5734</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4640,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699079</v>
+        <v>699060</v>
       </c>
       <c r="R41" t="n">
-        <v>6671615</v>
+        <v>6671608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4676,6 +4671,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3123,10 +3123,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B27" t="n">
-        <v>86906</v>
+        <v>87034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R27" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
         <v>129064614</v>
       </c>
       <c r="B28" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B29" t="n">
-        <v>87034</v>
+        <v>86906</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R29" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
         <v>129066734</v>
       </c>
       <c r="B30" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>90314</v>
+        <v>90317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129070090</v>
       </c>
       <c r="B37" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4383,32 +4383,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129070230</v>
+        <v>129068846</v>
       </c>
       <c r="B39" t="n">
-        <v>86982</v>
+        <v>86855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>249228</v>
+        <v>427</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699079</v>
+        <v>699044</v>
       </c>
       <c r="R39" t="n">
-        <v>6671615</v>
+        <v>6671620</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129068846</v>
+        <v>129068864</v>
       </c>
       <c r="B40" t="n">
-        <v>86855</v>
+        <v>91049</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,25 +4499,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>427</v>
+        <v>5734</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4526,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699044</v>
+        <v>699060</v>
       </c>
       <c r="R40" t="n">
-        <v>6671620</v>
+        <v>6671608</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,6 +4566,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4593,40 +4602,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129068864</v>
+        <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>91046</v>
+        <v>86982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5734</v>
+        <v>249228</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4635,10 +4640,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699060</v>
+        <v>699079</v>
       </c>
       <c r="R41" t="n">
-        <v>6671608</v>
+        <v>6671615</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,11 +4676,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4707,32 +4707,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B42" t="n">
-        <v>92821</v>
+        <v>87005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R42" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,32 +4812,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129068822</v>
+        <v>129066516</v>
       </c>
       <c r="B43" t="n">
-        <v>87005</v>
+        <v>92824</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699119</v>
+        <v>698988</v>
       </c>
       <c r="R43" t="n">
-        <v>6671545</v>
+        <v>6671638</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
         <v>129068561</v>
       </c>
       <c r="B44" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91086</v>
+        <v>91089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -2801,39 +2801,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129069986</v>
+        <v>129068659</v>
       </c>
       <c r="B24" t="n">
-        <v>43982</v>
+        <v>86897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2841,10 +2839,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699009</v>
+        <v>699037</v>
       </c>
       <c r="R24" t="n">
-        <v>6671637</v>
+        <v>6671604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2877,11 +2875,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2913,37 +2906,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129068659</v>
+        <v>129069986</v>
       </c>
       <c r="B25" t="n">
-        <v>86897</v>
+        <v>43982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>445</v>
+        <v>101735</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -2951,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699037</v>
+        <v>699009</v>
       </c>
       <c r="R25" t="n">
-        <v>6671604</v>
+        <v>6671637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2987,6 +2982,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B27" t="n">
-        <v>87034</v>
+        <v>86906</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3134,21 +3134,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R27" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B29" t="n">
-        <v>86906</v>
+        <v>87034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R29" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,32 +3858,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129069770</v>
+        <v>129070093</v>
       </c>
       <c r="B34" t="n">
-        <v>90317</v>
+        <v>92327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1595</v>
+        <v>232138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699009</v>
+        <v>699021</v>
       </c>
       <c r="R34" t="n">
-        <v>6671637</v>
+        <v>6671642</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3963,32 +3963,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129070093</v>
+        <v>129069770</v>
       </c>
       <c r="B35" t="n">
-        <v>92327</v>
+        <v>90317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>232138</v>
+        <v>1595</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699021</v>
+        <v>699009</v>
       </c>
       <c r="R35" t="n">
-        <v>6671642</v>
+        <v>6671637</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4383,32 +4383,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129068846</v>
+        <v>129070230</v>
       </c>
       <c r="B39" t="n">
-        <v>86855</v>
+        <v>86982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>427</v>
+        <v>249228</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699044</v>
+        <v>699079</v>
       </c>
       <c r="R39" t="n">
-        <v>6671620</v>
+        <v>6671615</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129068864</v>
+        <v>129068846</v>
       </c>
       <c r="B40" t="n">
-        <v>91049</v>
+        <v>86855</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4499,29 +4499,25 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5734</v>
+        <v>427</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4530,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699060</v>
+        <v>699044</v>
       </c>
       <c r="R40" t="n">
-        <v>6671608</v>
+        <v>6671620</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4566,11 +4562,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4602,36 +4593,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129070230</v>
+        <v>129068864</v>
       </c>
       <c r="B41" t="n">
-        <v>86982</v>
+        <v>91049</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249228</v>
+        <v>5734</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4640,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699079</v>
+        <v>699060</v>
       </c>
       <c r="R41" t="n">
-        <v>6671615</v>
+        <v>6671608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4676,6 +4671,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4707,32 +4707,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129068822</v>
+        <v>129066516</v>
       </c>
       <c r="B42" t="n">
-        <v>87005</v>
+        <v>92824</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>150</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699119</v>
+        <v>698988</v>
       </c>
       <c r="R42" t="n">
-        <v>6671545</v>
+        <v>6671638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4812,32 +4812,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129066516</v>
+        <v>129068822</v>
       </c>
       <c r="B43" t="n">
-        <v>92824</v>
+        <v>87005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>150</v>
+        <v>6003295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>698988</v>
+        <v>699119</v>
       </c>
       <c r="R43" t="n">
-        <v>6671638</v>
+        <v>6671545</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3228,32 +3228,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129064614</v>
+        <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>92824</v>
+        <v>87034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699036</v>
+        <v>699078</v>
       </c>
       <c r="R28" t="n">
-        <v>6671536</v>
+        <v>6671632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129068961</v>
+        <v>129064614</v>
       </c>
       <c r="B29" t="n">
-        <v>87034</v>
+        <v>92824</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3739</v>
+        <v>150</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699078</v>
+        <v>699036</v>
       </c>
       <c r="R29" t="n">
-        <v>6671632</v>
+        <v>6671536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4383,36 +4383,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129070230</v>
+        <v>129068864</v>
       </c>
       <c r="B39" t="n">
-        <v>86982</v>
+        <v>91049</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>249228</v>
+        <v>5734</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4421,10 +4425,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699079</v>
+        <v>699060</v>
       </c>
       <c r="R39" t="n">
-        <v>6671615</v>
+        <v>6671608</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4457,6 +4461,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4593,40 +4602,36 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129068864</v>
+        <v>129070230</v>
       </c>
       <c r="B41" t="n">
-        <v>91049</v>
+        <v>86982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5734</v>
+        <v>249228</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4635,10 +4640,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699060</v>
+        <v>699079</v>
       </c>
       <c r="R41" t="n">
-        <v>6671608</v>
+        <v>6671615</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,11 +4676,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -3123,32 +3123,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129067215</v>
+        <v>129064614</v>
       </c>
       <c r="B27" t="n">
-        <v>86906</v>
+        <v>92824</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3611</v>
+        <v>150</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698984</v>
+        <v>699036</v>
       </c>
       <c r="R27" t="n">
-        <v>6671633</v>
+        <v>6671536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129068961</v>
+        <v>129067215</v>
       </c>
       <c r="B28" t="n">
-        <v>87034</v>
+        <v>86906</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3739</v>
+        <v>3611</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699078</v>
+        <v>698984</v>
       </c>
       <c r="R28" t="n">
-        <v>6671632</v>
+        <v>6671633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129064614</v>
+        <v>129068961</v>
       </c>
       <c r="B29" t="n">
-        <v>92824</v>
+        <v>87034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699036</v>
+        <v>699078</v>
       </c>
       <c r="R29" t="n">
-        <v>6671536</v>
+        <v>6671632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,32 +3858,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129070093</v>
+        <v>129069770</v>
       </c>
       <c r="B34" t="n">
-        <v>92327</v>
+        <v>90317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>232138</v>
+        <v>1595</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699021</v>
+        <v>699009</v>
       </c>
       <c r="R34" t="n">
-        <v>6671642</v>
+        <v>6671637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3963,32 +3963,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129069770</v>
+        <v>129070093</v>
       </c>
       <c r="B35" t="n">
-        <v>90317</v>
+        <v>92327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1595</v>
+        <v>232138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699009</v>
+        <v>699021</v>
       </c>
       <c r="R35" t="n">
-        <v>6671637</v>
+        <v>6671642</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129068864</v>
+        <v>129068846</v>
       </c>
       <c r="B39" t="n">
-        <v>91049</v>
+        <v>86855</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4394,29 +4394,25 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5734</v>
+        <v>427</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius aureopulverulentus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4425,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699060</v>
+        <v>699044</v>
       </c>
       <c r="R39" t="n">
-        <v>6671608</v>
+        <v>6671620</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,11 +4457,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4497,32 +4488,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129068846</v>
+        <v>129070230</v>
       </c>
       <c r="B40" t="n">
-        <v>86855</v>
+        <v>86982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>427</v>
+        <v>249228</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4535,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699044</v>
+        <v>699079</v>
       </c>
       <c r="R40" t="n">
-        <v>6671620</v>
+        <v>6671615</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4602,36 +4593,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129070230</v>
+        <v>129068864</v>
       </c>
       <c r="B41" t="n">
-        <v>86982</v>
+        <v>91049</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>249228</v>
+        <v>5734</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4640,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699079</v>
+        <v>699060</v>
       </c>
       <c r="R41" t="n">
-        <v>6671615</v>
+        <v>6671608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4676,6 +4671,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växte med relativt unga granar och björkar.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91089</v>
+        <v>91117</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86897</v>
+        <v>86925</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91117</v>
+        <v>91123</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86925</v>
+        <v>86931</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86931</v>
+        <v>86932</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5025,7 +5025,7 @@
         <v>129066928</v>
       </c>
       <c r="B45" t="n">
-        <v>91124</v>
+        <v>91129</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>129068693</v>
       </c>
       <c r="B46" t="n">
-        <v>86932</v>
+        <v>86937</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5243,6 +5243,238 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130379953</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87079</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>699040</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6671418</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>3 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Grandominerad barr-/blandskog.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130379960</v>
+      </c>
+      <c r="B48" t="n">
+        <v>93028</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>699204</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6671281</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Grandominerad barr-/blandskog.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87079</v>
+        <v>87082</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93028</v>
+        <v>93031</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87082</v>
+        <v>87108</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93031</v>
+        <v>93057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87108</v>
+        <v>87109</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93057</v>
+        <v>93058</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87109</v>
+        <v>87110</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93058</v>
+        <v>93059</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87110</v>
+        <v>87112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93059</v>
+        <v>93061</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93061</v>
+        <v>93065</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87112</v>
+        <v>87122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93065</v>
+        <v>93078</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87122</v>
+        <v>87123</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93078</v>
+        <v>93079</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5248,7 +5248,7 @@
         <v>130379953</v>
       </c>
       <c r="B47" t="n">
-        <v>87123</v>
+        <v>87124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>130379960</v>
       </c>
       <c r="B48" t="n">
-        <v>93079</v>
+        <v>93080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5475,6 +5475,1724 @@
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131736816</v>
+      </c>
+      <c r="B49" t="n">
+        <v>93128</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>699008</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6671653</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131736814</v>
+      </c>
+      <c r="B50" t="n">
+        <v>93128</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vallmar Nordväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>699042</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6671411</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131740321</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>698943</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6671660</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131736815</v>
+      </c>
+      <c r="B52" t="n">
+        <v>93128</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bolviken Sydost, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>698984</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6671480</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131740034</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91328</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Pinkdal Nordost, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>699135</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6671424</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131740601</v>
+      </c>
+      <c r="B54" t="n">
+        <v>102154</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>698950</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6671639</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131737275</v>
+      </c>
+      <c r="B55" t="n">
+        <v>87067</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>699030</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6671657</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131740536</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87333</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>699030</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6671654</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131737280</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87067</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>699034</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6671599</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131737274</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87067</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>699008</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6671648</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131733600</v>
+      </c>
+      <c r="B59" t="n">
+        <v>87230</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vallmar Nordväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>699155</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6671396</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131737276</v>
+      </c>
+      <c r="B60" t="n">
+        <v>87067</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>699043</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6671647</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131737278</v>
+      </c>
+      <c r="B61" t="n">
+        <v>87067</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vallmar Nordväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>699148</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6671394</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131740317</v>
+      </c>
+      <c r="B62" t="n">
+        <v>111303</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>698952</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6671645</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131740600</v>
+      </c>
+      <c r="B63" t="n">
+        <v>102154</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bolviken Sydost, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>698989</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6671491</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131739801</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92551</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bolviken Syd, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>698947</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6671618</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131735751</v>
+      </c>
+      <c r="B65" t="n">
+        <v>44129</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vallmar Nordväst, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>699038</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6671430</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka. Björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6382,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737274</v>
+        <v>131733600</v>
       </c>
       <c r="B58" t="n">
-        <v>87067</v>
+        <v>87230</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,34 +6393,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699008</v>
+        <v>699155</v>
       </c>
       <c r="R58" t="n">
-        <v>6671648</v>
+        <v>6671396</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6483,10 +6483,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131733600</v>
+        <v>131737274</v>
       </c>
       <c r="B59" t="n">
-        <v>87230</v>
+        <v>87067</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6494,34 +6494,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699155</v>
+        <v>699008</v>
       </c>
       <c r="R59" t="n">
-        <v>6671396</v>
+        <v>6671648</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740317</v>
+        <v>131739801</v>
       </c>
       <c r="B62" t="n">
-        <v>111303</v>
+        <v>92551</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,21 +6797,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219711</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698952</v>
+        <v>698947</v>
       </c>
       <c r="R62" t="n">
-        <v>6671645</v>
+        <v>6671618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739801</v>
+        <v>131740317</v>
       </c>
       <c r="B64" t="n">
-        <v>92551</v>
+        <v>111303</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698947</v>
+        <v>698952</v>
       </c>
       <c r="R64" t="n">
-        <v>6671618</v>
+        <v>6671645</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>131736816</v>
       </c>
       <c r="B49" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131736814</v>
       </c>
       <c r="B50" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>131740321</v>
       </c>
       <c r="B51" t="n">
-        <v>92788</v>
+        <v>92789</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>131736815</v>
       </c>
       <c r="B52" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131740034</v>
       </c>
       <c r="B53" t="n">
-        <v>91328</v>
+        <v>91329</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102154</v>
+        <v>102155</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737275</v>
       </c>
       <c r="B55" t="n">
-        <v>87067</v>
+        <v>87068</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87333</v>
+        <v>87334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87067</v>
+        <v>87068</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131733600</v>
+        <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87230</v>
+        <v>87068</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,34 +6393,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699155</v>
+        <v>699008</v>
       </c>
       <c r="R58" t="n">
-        <v>6671396</v>
+        <v>6671648</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6483,10 +6483,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737274</v>
+        <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87067</v>
+        <v>87231</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6494,34 +6494,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699008</v>
+        <v>699155</v>
       </c>
       <c r="R59" t="n">
-        <v>6671648</v>
+        <v>6671396</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6587,7 +6587,7 @@
         <v>131737276</v>
       </c>
       <c r="B60" t="n">
-        <v>87067</v>
+        <v>87068</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>131737278</v>
       </c>
       <c r="B61" t="n">
-        <v>87067</v>
+        <v>87068</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>131739801</v>
       </c>
       <c r="B62" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131740600</v>
+        <v>131740317</v>
       </c>
       <c r="B63" t="n">
-        <v>102154</v>
+        <v>111304</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,34 +6898,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698989</v>
+        <v>698952</v>
       </c>
       <c r="R63" t="n">
-        <v>6671491</v>
+        <v>6671645</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740317</v>
+        <v>131740600</v>
       </c>
       <c r="B64" t="n">
-        <v>111303</v>
+        <v>102155</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698952</v>
+        <v>698989</v>
       </c>
       <c r="R64" t="n">
-        <v>6671645</v>
+        <v>6671491</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         <v>131735751</v>
       </c>
       <c r="B65" t="n">
-        <v>44129</v>
+        <v>44130</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>131736816</v>
       </c>
       <c r="B49" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131736814</v>
       </c>
       <c r="B50" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>131740321</v>
       </c>
       <c r="B51" t="n">
-        <v>92789</v>
+        <v>92792</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>131736815</v>
       </c>
       <c r="B52" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131740034</v>
       </c>
       <c r="B53" t="n">
-        <v>91329</v>
+        <v>91332</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102155</v>
+        <v>102157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737275</v>
       </c>
       <c r="B55" t="n">
-        <v>87068</v>
+        <v>87071</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87334</v>
+        <v>87337</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87068</v>
+        <v>87071</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87068</v>
+        <v>87071</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87231</v>
+        <v>87234</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131737276</v>
       </c>
       <c r="B60" t="n">
-        <v>87068</v>
+        <v>87071</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>131737278</v>
       </c>
       <c r="B61" t="n">
-        <v>87068</v>
+        <v>87071</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739801</v>
+        <v>131740600</v>
       </c>
       <c r="B62" t="n">
-        <v>92552</v>
+        <v>102157</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698947</v>
+        <v>698989</v>
       </c>
       <c r="R62" t="n">
-        <v>6671618</v>
+        <v>6671491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6890,7 +6890,7 @@
         <v>131740317</v>
       </c>
       <c r="B63" t="n">
-        <v>111304</v>
+        <v>111302</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740600</v>
+        <v>131739801</v>
       </c>
       <c r="B64" t="n">
-        <v>102155</v>
+        <v>92555</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698989</v>
+        <v>698947</v>
       </c>
       <c r="R64" t="n">
-        <v>6671491</v>
+        <v>6671618</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         <v>131735751</v>
       </c>
       <c r="B65" t="n">
-        <v>44130</v>
+        <v>44133</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102157</v>
+        <v>102158</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740600</v>
+        <v>131739801</v>
       </c>
       <c r="B62" t="n">
-        <v>102157</v>
+        <v>92555</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698989</v>
+        <v>698947</v>
       </c>
       <c r="R62" t="n">
-        <v>6671491</v>
+        <v>6671618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131740317</v>
+        <v>131740600</v>
       </c>
       <c r="B63" t="n">
-        <v>111302</v>
+        <v>102158</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,34 +6898,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698952</v>
+        <v>698989</v>
       </c>
       <c r="R63" t="n">
-        <v>6671645</v>
+        <v>6671491</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739801</v>
+        <v>131740317</v>
       </c>
       <c r="B64" t="n">
-        <v>92555</v>
+        <v>111303</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698947</v>
+        <v>698952</v>
       </c>
       <c r="R64" t="n">
-        <v>6671618</v>
+        <v>6671645</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739801</v>
+        <v>131740317</v>
       </c>
       <c r="B62" t="n">
-        <v>92555</v>
+        <v>111303</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,21 +6797,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>219711</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698947</v>
+        <v>698952</v>
       </c>
       <c r="R62" t="n">
-        <v>6671618</v>
+        <v>6671645</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131740600</v>
+        <v>131739801</v>
       </c>
       <c r="B63" t="n">
-        <v>102158</v>
+        <v>92555</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,34 +6898,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221235</v>
+        <v>3298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698989</v>
+        <v>698947</v>
       </c>
       <c r="R63" t="n">
-        <v>6671491</v>
+        <v>6671618</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740317</v>
+        <v>131740600</v>
       </c>
       <c r="B64" t="n">
-        <v>111303</v>
+        <v>102158</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698952</v>
+        <v>698989</v>
       </c>
       <c r="R64" t="n">
-        <v>6671645</v>
+        <v>6671491</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>131736816</v>
       </c>
       <c r="B49" t="n">
-        <v>93132</v>
+        <v>93138</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131736814</v>
       </c>
       <c r="B50" t="n">
-        <v>93132</v>
+        <v>93138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131740321</v>
+        <v>131736815</v>
       </c>
       <c r="B51" t="n">
-        <v>92792</v>
+        <v>93138</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>698943</v>
+        <v>698984</v>
       </c>
       <c r="R51" t="n">
-        <v>6671660</v>
+        <v>6671480</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131736815</v>
+        <v>131740321</v>
       </c>
       <c r="B52" t="n">
-        <v>93132</v>
+        <v>92798</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5791,34 +5791,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>698984</v>
+        <v>698943</v>
       </c>
       <c r="R52" t="n">
-        <v>6671480</v>
+        <v>6671660</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,7 +5884,7 @@
         <v>131740034</v>
       </c>
       <c r="B53" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102158</v>
+        <v>102164</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737275</v>
       </c>
       <c r="B55" t="n">
-        <v>87071</v>
+        <v>87077</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87337</v>
+        <v>87343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87071</v>
+        <v>87077</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87071</v>
+        <v>87077</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87234</v>
+        <v>87240</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131737276</v>
       </c>
       <c r="B60" t="n">
-        <v>87071</v>
+        <v>87077</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>131737278</v>
       </c>
       <c r="B61" t="n">
-        <v>87071</v>
+        <v>87077</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740317</v>
+        <v>131740600</v>
       </c>
       <c r="B62" t="n">
-        <v>111303</v>
+        <v>102164</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698952</v>
+        <v>698989</v>
       </c>
       <c r="R62" t="n">
-        <v>6671645</v>
+        <v>6671491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6890,7 +6890,7 @@
         <v>131739801</v>
       </c>
       <c r="B63" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740600</v>
+        <v>131740317</v>
       </c>
       <c r="B64" t="n">
-        <v>102158</v>
+        <v>111309</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698989</v>
+        <v>698952</v>
       </c>
       <c r="R64" t="n">
-        <v>6671491</v>
+        <v>6671645</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>131736816</v>
       </c>
       <c r="B49" t="n">
-        <v>93138</v>
+        <v>93141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131736814</v>
       </c>
       <c r="B50" t="n">
-        <v>93138</v>
+        <v>93141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131736815</v>
+        <v>131740321</v>
       </c>
       <c r="B51" t="n">
-        <v>93138</v>
+        <v>92801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>698984</v>
+        <v>698943</v>
       </c>
       <c r="R51" t="n">
-        <v>6671480</v>
+        <v>6671660</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131740321</v>
+        <v>131736815</v>
       </c>
       <c r="B52" t="n">
-        <v>92798</v>
+        <v>93141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5791,34 +5791,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>698943</v>
+        <v>698984</v>
       </c>
       <c r="R52" t="n">
-        <v>6671660</v>
+        <v>6671480</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5884,7 +5884,7 @@
         <v>131740034</v>
       </c>
       <c r="B53" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102164</v>
+        <v>102167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737275</v>
       </c>
       <c r="B55" t="n">
-        <v>87077</v>
+        <v>87080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87343</v>
+        <v>87346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87077</v>
+        <v>87080</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87077</v>
+        <v>87080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87240</v>
+        <v>87243</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131737276</v>
       </c>
       <c r="B60" t="n">
-        <v>87077</v>
+        <v>87080</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>131737278</v>
       </c>
       <c r="B61" t="n">
-        <v>87077</v>
+        <v>87080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740600</v>
+        <v>131740317</v>
       </c>
       <c r="B62" t="n">
-        <v>102164</v>
+        <v>111316</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698989</v>
+        <v>698952</v>
       </c>
       <c r="R62" t="n">
-        <v>6671491</v>
+        <v>6671645</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6890,7 +6890,7 @@
         <v>131739801</v>
       </c>
       <c r="B63" t="n">
-        <v>92561</v>
+        <v>92564</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740317</v>
+        <v>131740600</v>
       </c>
       <c r="B64" t="n">
-        <v>111309</v>
+        <v>102167</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698952</v>
+        <v>698989</v>
       </c>
       <c r="R64" t="n">
-        <v>6671645</v>
+        <v>6671491</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         <v>131735751</v>
       </c>
       <c r="B65" t="n">
-        <v>44133</v>
+        <v>44134</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>131736816</v>
       </c>
       <c r="B49" t="n">
-        <v>93141</v>
+        <v>93146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131736814</v>
       </c>
       <c r="B50" t="n">
-        <v>93141</v>
+        <v>93146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>131740321</v>
       </c>
       <c r="B51" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>131736815</v>
       </c>
       <c r="B52" t="n">
-        <v>93141</v>
+        <v>93146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131740034</v>
       </c>
       <c r="B53" t="n">
-        <v>91341</v>
+        <v>91346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102167</v>
+        <v>102172</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737275</v>
       </c>
       <c r="B55" t="n">
-        <v>87080</v>
+        <v>87085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87346</v>
+        <v>87351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87080</v>
+        <v>87085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87080</v>
+        <v>87085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87243</v>
+        <v>87248</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131737276</v>
       </c>
       <c r="B60" t="n">
-        <v>87080</v>
+        <v>87085</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>131737278</v>
       </c>
       <c r="B61" t="n">
-        <v>87080</v>
+        <v>87085</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740317</v>
+        <v>131739801</v>
       </c>
       <c r="B62" t="n">
-        <v>111316</v>
+        <v>92569</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,21 +6797,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219711</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698952</v>
+        <v>698947</v>
       </c>
       <c r="R62" t="n">
-        <v>6671645</v>
+        <v>6671618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739801</v>
+        <v>131740317</v>
       </c>
       <c r="B63" t="n">
-        <v>92564</v>
+        <v>111321</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,21 +6898,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>219711</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698947</v>
+        <v>698952</v>
       </c>
       <c r="R63" t="n">
-        <v>6671618</v>
+        <v>6671645</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6991,7 +6991,7 @@
         <v>131740600</v>
       </c>
       <c r="B64" t="n">
-        <v>102167</v>
+        <v>102172</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>131735751</v>
       </c>
       <c r="B65" t="n">
-        <v>44134</v>
+        <v>44137</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739801</v>
+        <v>131740600</v>
       </c>
       <c r="B62" t="n">
-        <v>92569</v>
+        <v>102172</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698947</v>
+        <v>698989</v>
       </c>
       <c r="R62" t="n">
-        <v>6671618</v>
+        <v>6671491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131740317</v>
+        <v>131739801</v>
       </c>
       <c r="B63" t="n">
-        <v>111321</v>
+        <v>92569</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,21 +6898,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219711</v>
+        <v>3298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698952</v>
+        <v>698947</v>
       </c>
       <c r="R63" t="n">
-        <v>6671645</v>
+        <v>6671618</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740600</v>
+        <v>131740317</v>
       </c>
       <c r="B64" t="n">
-        <v>102172</v>
+        <v>111321</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698989</v>
+        <v>698952</v>
       </c>
       <c r="R64" t="n">
-        <v>6671491</v>
+        <v>6671645</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>131736816</v>
       </c>
       <c r="B49" t="n">
-        <v>93146</v>
+        <v>93148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131736814</v>
       </c>
       <c r="B50" t="n">
-        <v>93146</v>
+        <v>93148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>131740321</v>
       </c>
       <c r="B51" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>131736815</v>
       </c>
       <c r="B52" t="n">
-        <v>93146</v>
+        <v>93148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131740034</v>
       </c>
       <c r="B53" t="n">
-        <v>91346</v>
+        <v>91348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102172</v>
+        <v>102175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737275</v>
       </c>
       <c r="B55" t="n">
-        <v>87085</v>
+        <v>87087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87351</v>
+        <v>87353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87085</v>
+        <v>87087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87085</v>
+        <v>87087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87248</v>
+        <v>87250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131737276</v>
       </c>
       <c r="B60" t="n">
-        <v>87085</v>
+        <v>87087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>131737278</v>
       </c>
       <c r="B61" t="n">
-        <v>87085</v>
+        <v>87087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>131740600</v>
       </c>
       <c r="B62" t="n">
-        <v>102172</v>
+        <v>102175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131739801</v>
       </c>
       <c r="B63" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>131740317</v>
       </c>
       <c r="B64" t="n">
-        <v>111321</v>
+        <v>111324</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>131735751</v>
       </c>
       <c r="B65" t="n">
-        <v>44137</v>
+        <v>44138</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740600</v>
+        <v>131740317</v>
       </c>
       <c r="B62" t="n">
-        <v>102175</v>
+        <v>111324</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698989</v>
+        <v>698952</v>
       </c>
       <c r="R62" t="n">
-        <v>6671491</v>
+        <v>6671645</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739801</v>
+        <v>131740600</v>
       </c>
       <c r="B63" t="n">
-        <v>92571</v>
+        <v>102175</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,34 +6898,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698947</v>
+        <v>698989</v>
       </c>
       <c r="R63" t="n">
-        <v>6671618</v>
+        <v>6671491</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740317</v>
+        <v>131739801</v>
       </c>
       <c r="B64" t="n">
-        <v>111324</v>
+        <v>92571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698952</v>
+        <v>698947</v>
       </c>
       <c r="R64" t="n">
-        <v>6671645</v>
+        <v>6671618</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740317</v>
+        <v>131739801</v>
       </c>
       <c r="B62" t="n">
-        <v>111324</v>
+        <v>92571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,21 +6797,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219711</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698952</v>
+        <v>698947</v>
       </c>
       <c r="R62" t="n">
-        <v>6671645</v>
+        <v>6671618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131740600</v>
+        <v>131740317</v>
       </c>
       <c r="B63" t="n">
-        <v>102175</v>
+        <v>111324</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,34 +6898,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698989</v>
+        <v>698952</v>
       </c>
       <c r="R63" t="n">
-        <v>6671491</v>
+        <v>6671645</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739801</v>
+        <v>131740600</v>
       </c>
       <c r="B64" t="n">
-        <v>92571</v>
+        <v>102175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698947</v>
+        <v>698989</v>
       </c>
       <c r="R64" t="n">
-        <v>6671618</v>
+        <v>6671491</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6184,10 +6184,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131740536</v>
+        <v>131737280</v>
       </c>
       <c r="B56" t="n">
-        <v>87353</v>
+        <v>87087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6195,19 +6195,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3624</v>
+        <v>3762</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6215,10 +6219,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699030</v>
+        <v>699034</v>
       </c>
       <c r="R56" t="n">
-        <v>6671654</v>
+        <v>6671599</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6281,10 +6285,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737280</v>
+        <v>131740536</v>
       </c>
       <c r="B57" t="n">
-        <v>87087</v>
+        <v>87353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6292,23 +6296,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3762</v>
+        <v>3624</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699034</v>
+        <v>699030</v>
       </c>
       <c r="R57" t="n">
-        <v>6671599</v>
+        <v>6671654</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6382,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737274</v>
+        <v>131733600</v>
       </c>
       <c r="B58" t="n">
-        <v>87087</v>
+        <v>87250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,34 +6393,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699008</v>
+        <v>699155</v>
       </c>
       <c r="R58" t="n">
-        <v>6671648</v>
+        <v>6671396</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6483,10 +6483,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131733600</v>
+        <v>131737274</v>
       </c>
       <c r="B59" t="n">
-        <v>87250</v>
+        <v>87087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6494,34 +6494,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699155</v>
+        <v>699008</v>
       </c>
       <c r="R59" t="n">
-        <v>6671396</v>
+        <v>6671648</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739801</v>
+        <v>131740600</v>
       </c>
       <c r="B62" t="n">
-        <v>92571</v>
+        <v>102175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698947</v>
+        <v>698989</v>
       </c>
       <c r="R62" t="n">
-        <v>6671618</v>
+        <v>6671491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740600</v>
+        <v>131739801</v>
       </c>
       <c r="B64" t="n">
-        <v>102175</v>
+        <v>92571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>3298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698989</v>
+        <v>698947</v>
       </c>
       <c r="R64" t="n">
-        <v>6671491</v>
+        <v>6671618</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6184,10 +6184,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131737280</v>
+        <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87087</v>
+        <v>87353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6195,23 +6195,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3762</v>
+        <v>3624</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6219,10 +6215,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699034</v>
+        <v>699030</v>
       </c>
       <c r="R56" t="n">
-        <v>6671599</v>
+        <v>6671654</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,10 +6281,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131740536</v>
+        <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87353</v>
+        <v>87087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6296,19 +6292,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3624</v>
+        <v>3762</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699030</v>
+        <v>699034</v>
       </c>
       <c r="R57" t="n">
-        <v>6671654</v>
+        <v>6671599</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6382,10 +6382,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131733600</v>
+        <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87250</v>
+        <v>87087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,34 +6393,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699155</v>
+        <v>699008</v>
       </c>
       <c r="R58" t="n">
-        <v>6671396</v>
+        <v>6671648</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6483,10 +6483,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131737274</v>
+        <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87087</v>
+        <v>87250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6494,34 +6494,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699008</v>
+        <v>699155</v>
       </c>
       <c r="R59" t="n">
-        <v>6671648</v>
+        <v>6671396</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740600</v>
+        <v>131739801</v>
       </c>
       <c r="B62" t="n">
-        <v>102175</v>
+        <v>92571</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698989</v>
+        <v>698947</v>
       </c>
       <c r="R62" t="n">
-        <v>6671491</v>
+        <v>6671618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131739801</v>
+        <v>131740600</v>
       </c>
       <c r="B64" t="n">
-        <v>92571</v>
+        <v>102175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698947</v>
+        <v>698989</v>
       </c>
       <c r="R64" t="n">
-        <v>6671618</v>
+        <v>6671491</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -5480,7 +5480,7 @@
         <v>131736816</v>
       </c>
       <c r="B49" t="n">
-        <v>93189</v>
+        <v>93192</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>131736814</v>
       </c>
       <c r="B50" t="n">
-        <v>93189</v>
+        <v>93192</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>131740321</v>
       </c>
       <c r="B51" t="n">
-        <v>92849</v>
+        <v>92852</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>131736815</v>
       </c>
       <c r="B52" t="n">
-        <v>93189</v>
+        <v>93192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>131740034</v>
       </c>
       <c r="B53" t="n">
-        <v>91389</v>
+        <v>91392</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>131740601</v>
       </c>
       <c r="B54" t="n">
-        <v>102216</v>
+        <v>102219</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>131737275</v>
       </c>
       <c r="B55" t="n">
-        <v>87128</v>
+        <v>87131</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>131740536</v>
       </c>
       <c r="B56" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>131737280</v>
       </c>
       <c r="B57" t="n">
-        <v>87128</v>
+        <v>87131</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>131737274</v>
       </c>
       <c r="B58" t="n">
-        <v>87128</v>
+        <v>87131</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>131733600</v>
       </c>
       <c r="B59" t="n">
-        <v>87291</v>
+        <v>87294</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>131737276</v>
       </c>
       <c r="B60" t="n">
-        <v>87128</v>
+        <v>87131</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>131737278</v>
       </c>
       <c r="B61" t="n">
-        <v>87128</v>
+        <v>87131</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>131740600</v>
       </c>
       <c r="B62" t="n">
-        <v>102216</v>
+        <v>102219</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131739801</v>
       </c>
       <c r="B63" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>131740317</v>
       </c>
       <c r="B64" t="n">
-        <v>111365</v>
+        <v>111368</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -6786,10 +6786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131740600</v>
+        <v>131739801</v>
       </c>
       <c r="B62" t="n">
-        <v>102219</v>
+        <v>92615</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,34 +6797,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698989</v>
+        <v>698947</v>
       </c>
       <c r="R62" t="n">
-        <v>6671491</v>
+        <v>6671618</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6887,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131739801</v>
+        <v>131740317</v>
       </c>
       <c r="B63" t="n">
-        <v>92615</v>
+        <v>111368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,21 +6898,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>219711</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698947</v>
+        <v>698952</v>
       </c>
       <c r="R63" t="n">
-        <v>6671618</v>
+        <v>6671645</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,10 +6988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740317</v>
+        <v>131740600</v>
       </c>
       <c r="B64" t="n">
-        <v>111368</v>
+        <v>102219</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +6999,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698952</v>
+        <v>698989</v>
       </c>
       <c r="R64" t="n">
-        <v>6671645</v>
+        <v>6671491</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128760342</v>
+        <v>128760338</v>
       </c>
       <c r="B2" t="n">
-        <v>92861</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699194</v>
+        <v>699211</v>
       </c>
       <c r="R2" t="n">
-        <v>6671305</v>
+        <v>6671286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128760348</v>
+        <v>128760350</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699166</v>
+        <v>699172</v>
       </c>
       <c r="R3" t="n">
-        <v>6671341</v>
+        <v>6671344</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128760352</v>
+        <v>129064614</v>
       </c>
       <c r="B4" t="n">
-        <v>92480</v>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699154</v>
+        <v>699036</v>
       </c>
       <c r="R4" t="n">
-        <v>6671353</v>
+        <v>6671536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -948,63 +951,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128760344</v>
+        <v>129066516</v>
       </c>
       <c r="B5" t="n">
-        <v>92831</v>
+        <v>93186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699192</v>
+        <v>698988</v>
       </c>
       <c r="R5" t="n">
-        <v>6671306</v>
+        <v>6671638</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1042,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1045,28 +1056,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128760349</v>
+        <v>129066718</v>
       </c>
       <c r="B6" t="n">
-        <v>91074</v>
+        <v>93186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1090,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5747</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699177</v>
+        <v>699049</v>
       </c>
       <c r="R6" t="n">
-        <v>6671345</v>
+        <v>6671663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1142,63 +1161,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128760345</v>
+        <v>129066734</v>
       </c>
       <c r="B7" t="n">
-        <v>86795</v>
+        <v>93186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>150</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699184</v>
+        <v>699028</v>
       </c>
       <c r="R7" t="n">
-        <v>6671328</v>
+        <v>6671663</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1239,63 +1266,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128760358</v>
+        <v>129068846</v>
       </c>
       <c r="B8" t="n">
-        <v>101771</v>
+        <v>87196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>427</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699099</v>
+        <v>699044</v>
       </c>
       <c r="R8" t="n">
-        <v>6671403</v>
+        <v>6671620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1336,66 +1371,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128760340</v>
+        <v>130379956</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>87196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>427</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699213</v>
+        <v>699079</v>
       </c>
       <c r="R9" t="n">
-        <v>6671287</v>
+        <v>6671372</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1419,12 +1468,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 ex. i barrmatta under gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1435,61 +1489,69 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grandominerad barr-/blandskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128760356</v>
+        <v>129068659</v>
       </c>
       <c r="B10" t="n">
-        <v>86795</v>
+        <v>87238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699154</v>
+        <v>699037</v>
       </c>
       <c r="R10" t="n">
-        <v>6671383</v>
+        <v>6671604</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1578,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1530,63 +1592,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128760357</v>
+        <v>129068693</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>87238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699153</v>
+        <v>698993</v>
       </c>
       <c r="R11" t="n">
-        <v>6671384</v>
+        <v>6671484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1613,12 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1627,28 +1697,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128760350</v>
+        <v>128934471</v>
       </c>
       <c r="B12" t="n">
-        <v>92824</v>
+        <v>91436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,34 +1731,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>1357</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699172</v>
+        <v>698917</v>
       </c>
       <c r="R12" t="n">
-        <v>6671344</v>
+        <v>6671640</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1710,12 +1788,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Intill även gul lammticka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1724,28 +1807,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128760338</v>
+        <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>92824</v>
+        <v>91436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,34 +1841,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>1357</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699211</v>
+        <v>698918</v>
       </c>
       <c r="R13" t="n">
-        <v>6671286</v>
+        <v>6671634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1807,12 +1898,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1821,63 +1912,79 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128760346</v>
+        <v>129066928</v>
       </c>
       <c r="B14" t="n">
-        <v>91063</v>
+        <v>91436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5733</v>
+        <v>1357</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699179</v>
+        <v>699058</v>
       </c>
       <c r="R14" t="n">
-        <v>6671330</v>
+        <v>6671601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +2011,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1918,63 +2030,77 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128760354</v>
+        <v>440789</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>101947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>1449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Häverö Vallmarsgården, 250 m V-ut, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699138</v>
+        <v>699089</v>
       </c>
       <c r="R15" t="n">
-        <v>6671369</v>
+        <v>6671136</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2127,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2008-05-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2008-05-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>12J4a. Tidigare angiven med 6671000 1654350 ± 10 m. Västliga delen av lokalen spolierad</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2017,61 +2148,73 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>båthusområde</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Floraväkteri AB-län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128760341</v>
+        <v>129069730</v>
       </c>
       <c r="B16" t="n">
-        <v>91074</v>
+        <v>90663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5747</v>
+        <v>1595</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699200</v>
+        <v>698919</v>
       </c>
       <c r="R16" t="n">
-        <v>6671298</v>
+        <v>6671640</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2098,12 +2241,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2112,63 +2255,71 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128760347</v>
+        <v>129069770</v>
       </c>
       <c r="B17" t="n">
-        <v>87023</v>
+        <v>90663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3739</v>
+        <v>1595</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699178</v>
+        <v>699009</v>
       </c>
       <c r="R17" t="n">
-        <v>6671333</v>
+        <v>6671637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2346,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2209,28 +2360,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128760359</v>
+        <v>131739801</v>
       </c>
       <c r="B18" t="n">
-        <v>98712</v>
+        <v>92199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,34 +2394,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699100</v>
+        <v>698947</v>
       </c>
       <c r="R18" t="n">
-        <v>6671402</v>
+        <v>6671618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2448,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2312,22 +2468,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128760355</v>
+        <v>128760360</v>
       </c>
       <c r="B19" t="n">
-        <v>86994</v>
+        <v>87247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,34 +2495,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>3611</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699151</v>
+        <v>699153</v>
       </c>
       <c r="R19" t="n">
-        <v>6671385</v>
+        <v>6671399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2403,7 +2567,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2422,45 +2585,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128760339</v>
+        <v>129067215</v>
       </c>
       <c r="B20" t="n">
-        <v>92871</v>
+        <v>87247</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699211</v>
+        <v>698984</v>
       </c>
       <c r="R20" t="n">
-        <v>6671286</v>
+        <v>6671633</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2487,12 +2653,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2501,63 +2667,71 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128760353</v>
+        <v>129067444</v>
       </c>
       <c r="B21" t="n">
-        <v>100772</v>
+        <v>87247</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>3611</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699156</v>
+        <v>698998</v>
       </c>
       <c r="R21" t="n">
-        <v>6671355</v>
+        <v>6671470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2584,12 +2758,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2598,28 +2772,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128760351</v>
+        <v>129067850</v>
       </c>
       <c r="B22" t="n">
-        <v>91035</v>
+        <v>87247</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2627,30 +2806,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5734</v>
+        <v>3611</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699161</v>
+        <v>699075</v>
       </c>
       <c r="R22" t="n">
-        <v>6671349</v>
+        <v>6671620</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2677,12 +2863,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2691,28 +2877,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128883852</v>
+        <v>129067907</v>
       </c>
       <c r="B23" t="n">
-        <v>91961</v>
+        <v>87247</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2720,29 +2911,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040162</v>
+        <v>3611</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699201</v>
+        <v>699076</v>
       </c>
       <c r="R23" t="n">
-        <v>6671236</v>
+        <v>6671622</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2769,12 +2968,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2783,69 +2982,80 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129068659</v>
+        <v>130379953</v>
       </c>
       <c r="B24" t="n">
-        <v>86897</v>
+        <v>87247</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>445</v>
+        <v>3611</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699037</v>
+        <v>699040</v>
       </c>
       <c r="R24" t="n">
-        <v>6671604</v>
+        <v>6671418</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2869,12 +3079,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3 ex. under gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2883,33 +3098,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Grandominerad barr-/blandskog.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129069986</v>
+        <v>131740536</v>
       </c>
       <c r="B25" t="n">
-        <v>43982</v>
+        <v>87474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,39 +3132,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101735</v>
+        <v>3624</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699009</v>
+        <v>699030</v>
       </c>
       <c r="R25" t="n">
-        <v>6671637</v>
+        <v>6671654</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2984,82 +3190,73 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129067850</v>
+        <v>131733600</v>
       </c>
       <c r="B26" t="n">
-        <v>86906</v>
+        <v>87371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3611</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699075</v>
+        <v>699155</v>
       </c>
       <c r="R26" t="n">
-        <v>6671620</v>
+        <v>6671396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,71 +3297,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129064614</v>
+        <v>128760347</v>
       </c>
       <c r="B27" t="n">
-        <v>92824</v>
+        <v>87375</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>150</v>
+        <v>3739</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699036</v>
+        <v>699178</v>
       </c>
       <c r="R27" t="n">
-        <v>6671536</v>
+        <v>6671333</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3191,12 +3384,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3205,33 +3398,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129067215</v>
+        <v>129068961</v>
       </c>
       <c r="B28" t="n">
-        <v>86906</v>
+        <v>87375</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3427,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3611</v>
+        <v>3739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3266,10 +3454,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698984</v>
+        <v>699078</v>
       </c>
       <c r="R28" t="n">
-        <v>6671633</v>
+        <v>6671632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,16 +3515,16 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129068961</v>
+        <v>129068964</v>
       </c>
       <c r="B29" t="n">
-        <v>87034</v>
+        <v>87375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3371,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699078</v>
+        <v>699076</v>
       </c>
       <c r="R29" t="n">
-        <v>6671632</v>
+        <v>6671622</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,54 +3620,51 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129066734</v>
+        <v>128760345</v>
       </c>
       <c r="B30" t="n">
-        <v>92824</v>
+        <v>87146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699028</v>
+        <v>699184</v>
       </c>
       <c r="R30" t="n">
-        <v>6671663</v>
+        <v>6671328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3506,12 +3691,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3520,71 +3705,63 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129068748</v>
+        <v>128760356</v>
       </c>
       <c r="B31" t="n">
-        <v>87005</v>
+        <v>87146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698990</v>
+        <v>699154</v>
       </c>
       <c r="R31" t="n">
-        <v>6671640</v>
+        <v>6671383</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3611,12 +3788,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3625,68 +3802,60 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129068763</v>
+        <v>131737274</v>
       </c>
       <c r="B32" t="n">
-        <v>87005</v>
+        <v>87208</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699044</v>
+        <v>699008</v>
       </c>
       <c r="R32" t="n">
         <v>6671648</v>
@@ -3730,71 +3899,67 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129067444</v>
+        <v>131737275</v>
       </c>
       <c r="B33" t="n">
-        <v>86906</v>
+        <v>87208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3611</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>698998</v>
+        <v>699030</v>
       </c>
       <c r="R33" t="n">
-        <v>6671470</v>
+        <v>6671657</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3835,33 +4000,32 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129069770</v>
+        <v>131737276</v>
       </c>
       <c r="B34" t="n">
-        <v>90317</v>
+        <v>87208</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,37 +4033,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1595</v>
+        <v>3762</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699009</v>
+        <v>699043</v>
       </c>
       <c r="R34" t="n">
-        <v>6671637</v>
+        <v>6671647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,71 +4101,67 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129070093</v>
+        <v>131737278</v>
       </c>
       <c r="B35" t="n">
-        <v>92327</v>
+        <v>87208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699021</v>
+        <v>699148</v>
       </c>
       <c r="R35" t="n">
-        <v>6671642</v>
+        <v>6671394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4045,71 +4202,67 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129068964</v>
+        <v>131737280</v>
       </c>
       <c r="B36" t="n">
-        <v>87034</v>
+        <v>87208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3739</v>
+        <v>3762</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699076</v>
+        <v>699034</v>
       </c>
       <c r="R36" t="n">
-        <v>6671622</v>
+        <v>6671599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4150,55 +4303,54 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129070090</v>
+        <v>129068561</v>
       </c>
       <c r="B37" t="n">
-        <v>92327</v>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>232138</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4211,10 +4363,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>698978</v>
+        <v>698941</v>
       </c>
       <c r="R37" t="n">
-        <v>6671642</v>
+        <v>6671657</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4272,54 +4424,51 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129067907</v>
+        <v>128760344</v>
       </c>
       <c r="B38" t="n">
-        <v>86906</v>
+        <v>93193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3611</v>
+        <v>4363</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699076</v>
+        <v>699192</v>
       </c>
       <c r="R38" t="n">
-        <v>6671622</v>
+        <v>6671306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4346,12 +4495,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4360,33 +4509,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129068846</v>
+        <v>128760340</v>
       </c>
       <c r="B39" t="n">
-        <v>86855</v>
+        <v>93209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4394,37 +4538,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>427</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699044</v>
+        <v>699213</v>
       </c>
       <c r="R39" t="n">
-        <v>6671620</v>
+        <v>6671287</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4451,12 +4592,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4465,71 +4606,63 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129070230</v>
+        <v>131736814</v>
       </c>
       <c r="B40" t="n">
-        <v>86982</v>
+        <v>93283</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>249228</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699079</v>
+        <v>699042</v>
       </c>
       <c r="R40" t="n">
-        <v>6671615</v>
+        <v>6671411</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4570,33 +4703,32 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129068864</v>
+        <v>131736815</v>
       </c>
       <c r="B41" t="n">
-        <v>91049</v>
+        <v>93283</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4604,41 +4736,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5734</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699060</v>
+        <v>698984</v>
       </c>
       <c r="R41" t="n">
-        <v>6671608</v>
+        <v>6671480</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4673,82 +4798,73 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växte med relativt unga granar och björkar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129066516</v>
+        <v>131736816</v>
       </c>
       <c r="B42" t="n">
-        <v>92824</v>
+        <v>93283</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>698988</v>
+        <v>699008</v>
       </c>
       <c r="R42" t="n">
-        <v>6671638</v>
+        <v>6671653</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,33 +4905,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129068822</v>
+        <v>130379960</v>
       </c>
       <c r="B43" t="n">
-        <v>87005</v>
+        <v>93215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,40 +4938,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>4368</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699119</v>
+        <v>699204</v>
       </c>
       <c r="R43" t="n">
-        <v>6671545</v>
+        <v>6671281</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4880,12 +5001,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 ex. under gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,71 +5020,68 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grandominerad barr-/blandskog.</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129068561</v>
+        <v>128760352</v>
       </c>
       <c r="B44" t="n">
-        <v>92827</v>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>698941</v>
+        <v>699154</v>
       </c>
       <c r="R44" t="n">
-        <v>6671657</v>
+        <v>6671353</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,12 +5108,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,79 +5122,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129066928</v>
+        <v>131740321</v>
       </c>
       <c r="B45" t="n">
-        <v>91129</v>
+        <v>92943</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1357</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699058</v>
+        <v>698943</v>
       </c>
       <c r="R45" t="n">
-        <v>6671601</v>
+        <v>6671660</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5106,82 +5213,73 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129068693</v>
+        <v>128760342</v>
       </c>
       <c r="B46" t="n">
-        <v>86937</v>
+        <v>93223</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>445</v>
+        <v>5448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>698993</v>
+        <v>699194</v>
       </c>
       <c r="R46" t="n">
-        <v>6671484</v>
+        <v>6671305</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5208,12 +5306,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5222,33 +5320,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130379953</v>
+        <v>128760346</v>
       </c>
       <c r="B47" t="n">
-        <v>87124</v>
+        <v>91424</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5256,46 +5349,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3611</v>
+        <v>5733</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699040</v>
+        <v>699179</v>
       </c>
       <c r="R47" t="n">
-        <v>6671418</v>
+        <v>6671330</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5319,17 +5403,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>3 ex. under gran.</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5340,31 +5419,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Grandominerad barr-/blandskog.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130379960</v>
+        <v>131740034</v>
       </c>
       <c r="B48" t="n">
-        <v>93089</v>
+        <v>91474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,46 +5446,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>5741</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
+          <t>Pinkdal Nordost, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699204</v>
+        <v>699135</v>
       </c>
       <c r="R48" t="n">
-        <v>6671281</v>
+        <v>6671424</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5435,17 +5500,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 ex. under gran.</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5456,66 +5516,65 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Grandominerad barr-/blandskog.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131736816</v>
+        <v>128760341</v>
       </c>
       <c r="B49" t="n">
-        <v>93192</v>
+        <v>91435</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4366</v>
+        <v>5747</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699008</v>
+        <v>699200</v>
       </c>
       <c r="R49" t="n">
-        <v>6671653</v>
+        <v>6671298</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5542,12 +5601,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5562,61 +5621,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131736814</v>
+        <v>128760349</v>
       </c>
       <c r="B50" t="n">
-        <v>93192</v>
+        <v>91435</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699042</v>
+        <v>699177</v>
       </c>
       <c r="R50" t="n">
-        <v>6671411</v>
+        <v>6671345</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5643,12 +5698,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5663,61 +5718,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131740321</v>
+        <v>128760339</v>
       </c>
       <c r="B51" t="n">
-        <v>92852</v>
+        <v>93233</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>698943</v>
+        <v>699211</v>
       </c>
       <c r="R51" t="n">
-        <v>6671660</v>
+        <v>6671286</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5744,12 +5795,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5764,61 +5815,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131736815</v>
+        <v>128760348</v>
       </c>
       <c r="B52" t="n">
-        <v>93192</v>
+        <v>93233</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>698984</v>
+        <v>699166</v>
       </c>
       <c r="R52" t="n">
-        <v>6671480</v>
+        <v>6671341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5845,12 +5892,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5865,61 +5912,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131740034</v>
+        <v>128760354</v>
       </c>
       <c r="B53" t="n">
-        <v>91392</v>
+        <v>93233</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Pinkdal Nordost, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699135</v>
+        <v>699138</v>
       </c>
       <c r="R53" t="n">
-        <v>6671424</v>
+        <v>6671369</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5946,12 +5989,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5966,26 +6009,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131740601</v>
+        <v>129069986</v>
       </c>
       <c r="B54" t="n">
-        <v>102219</v>
+        <v>44177</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5993,34 +6032,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221235</v>
+        <v>101735</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>698950</v>
+        <v>699009</v>
       </c>
       <c r="R54" t="n">
-        <v>6671639</v>
+        <v>6671637</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6055,19 +6099,25 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -6083,10 +6133,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131737275</v>
+        <v>131735751</v>
       </c>
       <c r="B55" t="n">
-        <v>87131</v>
+        <v>44182</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6094,34 +6144,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3762</v>
+        <v>101735</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>699030</v>
+        <v>699038</v>
       </c>
       <c r="R55" t="n">
-        <v>6671657</v>
+        <v>6671430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6154,6 +6204,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka. Björkhögstubbe.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6184,30 +6239,34 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131740536</v>
+        <v>131740317</v>
       </c>
       <c r="B56" t="n">
-        <v>87397</v>
+        <v>111471</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3624</v>
+        <v>219711</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6215,10 +6274,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699030</v>
+        <v>698952</v>
       </c>
       <c r="R56" t="n">
-        <v>6671654</v>
+        <v>6671645</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6281,10 +6340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131737280</v>
+        <v>105310328</v>
       </c>
       <c r="B57" t="n">
-        <v>87131</v>
+        <v>99096</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6292,37 +6351,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3762</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699034</v>
+        <v>699290</v>
       </c>
       <c r="R57" t="n">
-        <v>6671599</v>
+        <v>6671272</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6346,12 +6405,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6362,6 +6421,16 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>3 plantor</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6374,18 +6443,14 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131737274</v>
+        <v>128760357</v>
       </c>
       <c r="B58" t="n">
-        <v>87131</v>
+        <v>99153</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6393,34 +6458,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3762</v>
+        <v>219874</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699008</v>
+        <v>699153</v>
       </c>
       <c r="R58" t="n">
-        <v>6671648</v>
+        <v>6671384</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6447,12 +6512,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6467,26 +6532,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131733600</v>
+        <v>128760359</v>
       </c>
       <c r="B59" t="n">
-        <v>87294</v>
+        <v>99153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6494,34 +6555,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3674</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699155</v>
+        <v>699100</v>
       </c>
       <c r="R59" t="n">
-        <v>6671396</v>
+        <v>6671402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6548,12 +6609,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6568,61 +6629,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131737276</v>
+        <v>128760358</v>
       </c>
       <c r="B60" t="n">
-        <v>87131</v>
+        <v>102240</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3762</v>
+        <v>221235</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>699043</v>
+        <v>699099</v>
       </c>
       <c r="R60" t="n">
-        <v>6671647</v>
+        <v>6671403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6649,12 +6706,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6669,61 +6726,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131737278</v>
+        <v>131740600</v>
       </c>
       <c r="B61" t="n">
-        <v>87131</v>
+        <v>102318</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3762</v>
+        <v>221235</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>699148</v>
+        <v>698989</v>
       </c>
       <c r="R61" t="n">
-        <v>6671394</v>
+        <v>6671491</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6786,32 +6839,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131739801</v>
+        <v>131740601</v>
       </c>
       <c r="B62" t="n">
-        <v>92615</v>
+        <v>102318</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6821,10 +6874,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>698947</v>
+        <v>698950</v>
       </c>
       <c r="R62" t="n">
-        <v>6671618</v>
+        <v>6671639</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6887,10 +6940,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131740317</v>
+        <v>105310331</v>
       </c>
       <c r="B63" t="n">
-        <v>111368</v>
+        <v>101326</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,37 +6951,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>698952</v>
+        <v>699257</v>
       </c>
       <c r="R63" t="n">
-        <v>6671645</v>
+        <v>6671312</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6952,12 +7005,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6968,6 +7021,11 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -6980,18 +7038,14 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131740600</v>
+        <v>128760353</v>
       </c>
       <c r="B64" t="n">
-        <v>102219</v>
+        <v>101227</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,34 +7053,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698989</v>
+        <v>699156</v>
       </c>
       <c r="R64" t="n">
-        <v>6671491</v>
+        <v>6671355</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7053,12 +7107,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7073,61 +7127,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131735751</v>
+        <v>128934451</v>
       </c>
       <c r="B65" t="n">
-        <v>44172</v>
+        <v>92688</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>101735</v>
+        <v>232138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>699038</v>
+        <v>698916</v>
       </c>
       <c r="R65" t="n">
-        <v>6671430</v>
+        <v>6671640</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7154,17 +7207,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Spår i fnösketicka. Björkhögstubbe.</t>
+          <t>Även fläckfingersvamp i direkt närhet.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7173,13 +7226,14 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -7188,6 +7242,1141 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129070080</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>698918</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6671642</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129070090</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>698978</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6671642</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129070093</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>699021</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6671642</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129070230</v>
+      </c>
+      <c r="B69" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>699079</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6671615</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128760355</v>
+      </c>
+      <c r="B70" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>699151</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6671385</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129068748</v>
+      </c>
+      <c r="B71" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>698990</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6671640</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129068763</v>
+      </c>
+      <c r="B72" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>699044</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6671648</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129068822</v>
+      </c>
+      <c r="B73" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>699119</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6671545</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128883852</v>
+      </c>
+      <c r="B74" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>699201</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6671236</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129069258</v>
+      </c>
+      <c r="B75" t="n">
+        <v>93224</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6331651</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Phellodon melilotinus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Quél.) Svantesson</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>699009</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6671637</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129070007</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>699032</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6671609</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129066516</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129066718</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129066734</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068846</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130379956</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068659</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068693</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934471</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129066767</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129066928</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2168,6 +2238,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Floraväkteri AB-län</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/440789</t>
         </is>
       </c>
     </row>
@@ -2275,6 +2350,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129069730</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2380,6 +2460,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129069770</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2481,6 +2566,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739801</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2582,6 +2672,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760360</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2687,6 +2782,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129067215</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129067444</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2897,6 +3002,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129067850</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3002,6 +3112,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129067907</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3118,6 +3233,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130379953</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3215,6 +3335,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740536</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3316,6 +3441,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733600</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3413,6 +3543,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760347</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3518,6 +3653,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068961</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3623,6 +3763,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068964</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3720,6 +3865,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760345</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3817,6 +3967,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760356</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3918,6 +4073,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737274</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4019,6 +4179,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737275</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4120,6 +4285,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737276</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4221,6 +4391,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737278</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4320,6 +4495,11 @@
       <c r="AY36" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737280</t>
         </is>
       </c>
     </row>
@@ -4427,6 +4607,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068561</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4524,6 +4709,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760344</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4621,6 +4811,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760340</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4722,6 +4917,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736814</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4823,6 +5023,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736815</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4924,6 +5129,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736816</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5040,6 +5250,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130379960</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5137,6 +5352,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760352</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5238,6 +5458,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740321</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5335,6 +5560,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760342</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5432,6 +5662,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760346</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5533,6 +5768,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740034</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5630,6 +5870,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760341</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5727,6 +5972,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760349</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5824,6 +6074,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760339</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5921,6 +6176,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760348</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6018,6 +6278,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760354</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6130,6 +6395,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129069986</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6236,6 +6506,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735751</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6337,6 +6612,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740317</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6444,6 +6724,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310328</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6541,6 +6826,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760357</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6638,6 +6928,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760359</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6735,6 +7030,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760358</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6836,6 +7136,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740600</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6937,6 +7242,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740601</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7039,6 +7349,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310331</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7136,6 +7451,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760353</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7246,6 +7566,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128934451</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7351,6 +7676,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070080</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7456,6 +7786,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070090</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7561,6 +7896,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070093</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7666,6 +8006,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070230</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7764,6 +8109,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760355</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7869,6 +8219,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068748</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7974,6 +8329,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068763</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8079,6 +8439,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129068822</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8176,6 +8541,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883852</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8276,6 +8646,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129069258</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8381,8 +8756,90 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129070007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ75"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129066928</v>
+        <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91436</v>
+        <v>91573</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,16 +1918,8 @@
           <t>(Pers.) Quél.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1936,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699058</v>
+        <v>698918</v>
       </c>
       <c r="R13" t="n">
-        <v>6671601</v>
+        <v>6671634</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,11 +1966,6 @@
           <t>2025-10-10</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2007,16 +1994,16 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129066928</t>
+          <t>https://artportalen.se/Sighting/129066767</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>440789</v>
+        <v>129066928</v>
       </c>
       <c r="B14" t="n">
-        <v>101947</v>
+        <v>91436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,43 +2011,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1449</v>
+        <v>1357</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hällebräcka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saxifraga osloënsis</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Knaben</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Häverö Vallmarsgården, 250 m V-ut, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699089</v>
+        <v>699058</v>
       </c>
       <c r="R14" t="n">
-        <v>6671136</v>
+        <v>6671601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,17 +2076,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2008-05-14</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2008-05-14</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>12J4a. Tidigare angiven med 6671000 1654350 ± 10 m. Västliga delen av lokalen spolierad</t>
+          <t>Tillsammans med två andra ramarior. En druvfingersvamp samt en okänd korallfingersvamp som var brunare.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,80 +2095,82 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>båthusområde</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Floraväkteri AB-län</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/440789</t>
+          <t>https://artportalen.se/Sighting/129066928</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129069730</v>
+        <v>440789</v>
       </c>
       <c r="B15" t="n">
-        <v>90663</v>
+        <v>101947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1595</v>
+        <v>1449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Häverö Vallmarsgården, 250 m V-ut, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698919</v>
+        <v>699089</v>
       </c>
       <c r="R15" t="n">
-        <v>6671640</v>
+        <v>6671136</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,12 +2197,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2008-05-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2008-05-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>12J4a. Tidigare angiven med 6671000 1654350 ± 10 m. Västliga delen av lokalen spolierad</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,35 +2216,39 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>båthusområde</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Floraväkteri AB-län</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129069730</t>
+          <t>https://artportalen.se/Sighting/440789</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129069770</v>
+        <v>129069730</v>
       </c>
       <c r="B16" t="n">
         <v>90663</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699009</v>
+        <v>698919</v>
       </c>
       <c r="R16" t="n">
-        <v>6671637</v>
+        <v>6671640</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,16 +2352,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129069770</t>
+          <t>https://artportalen.se/Sighting/129069730</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131739801</v>
+        <v>129069770</v>
       </c>
       <c r="B17" t="n">
-        <v>92199</v>
+        <v>90663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,34 +2369,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1595</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698947</v>
+        <v>699009</v>
       </c>
       <c r="R17" t="n">
-        <v>6671618</v>
+        <v>6671637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,13 +2440,14 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2458,55 +2462,51 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131739801</t>
+          <t>https://artportalen.se/Sighting/129069770</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128760360</v>
+        <v>131739801</v>
       </c>
       <c r="B18" t="n">
-        <v>87247</v>
+        <v>92199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3611</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699153</v>
+        <v>698947</v>
       </c>
       <c r="R18" t="n">
-        <v>6671399</v>
+        <v>6671618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,24 +2553,28 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760360</t>
+          <t>https://artportalen.se/Sighting/131739801</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129067215</v>
+        <v>128760360</v>
       </c>
       <c r="B19" t="n">
         <v>87247</v>
@@ -2598,20 +2602,21 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698984</v>
+        <v>699153</v>
       </c>
       <c r="R19" t="n">
-        <v>6671633</v>
+        <v>6671399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,12 +2643,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,35 +2657,30 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129067215</t>
+          <t>https://artportalen.se/Sighting/128760360</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129067444</v>
+        <v>129067215</v>
       </c>
       <c r="B20" t="n">
         <v>87247</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698998</v>
+        <v>698984</v>
       </c>
       <c r="R20" t="n">
-        <v>6671470</v>
+        <v>6671633</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,13 +2784,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129067444</t>
+          <t>https://artportalen.se/Sighting/129067215</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129067850</v>
+        <v>129067444</v>
       </c>
       <c r="B21" t="n">
         <v>87247</v>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699075</v>
+        <v>698998</v>
       </c>
       <c r="R21" t="n">
-        <v>6671620</v>
+        <v>6671470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2894,13 +2894,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129067850</t>
+          <t>https://artportalen.se/Sighting/129067444</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129067907</v>
+        <v>129067850</v>
       </c>
       <c r="B22" t="n">
         <v>87247</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699076</v>
+        <v>699075</v>
       </c>
       <c r="R22" t="n">
-        <v>6671622</v>
+        <v>6671620</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3004,13 +3004,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129067907</t>
+          <t>https://artportalen.se/Sighting/129067850</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130379953</v>
+        <v>129067907</v>
       </c>
       <c r="B23" t="n">
         <v>87247</v>
@@ -3038,29 +3038,23 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699040</v>
+        <v>699076</v>
       </c>
       <c r="R23" t="n">
-        <v>6671418</v>
+        <v>6671622</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3084,17 +3078,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>3 ex. under gran.</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3103,72 +3092,85 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grandominerad barr-/blandskog.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379953</t>
+          <t>https://artportalen.se/Sighting/129067907</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131740536</v>
+        <v>130379953</v>
       </c>
       <c r="B24" t="n">
-        <v>87474</v>
+        <v>87247</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3624</v>
+        <v>3611</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699030</v>
+        <v>699040</v>
       </c>
       <c r="R24" t="n">
-        <v>6671654</v>
+        <v>6671418</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,12 +3194,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3 ex. under gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3208,35 +3215,36 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Grandominerad barr-/blandskog.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740536</t>
+          <t>https://artportalen.se/Sighting/130379953</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131733600</v>
+        <v>131740536</v>
       </c>
       <c r="B25" t="n">
-        <v>87371</v>
+        <v>87474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3244,34 +3252,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699155</v>
+        <v>699030</v>
       </c>
       <c r="R25" t="n">
-        <v>6671396</v>
+        <v>6671654</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,51 +3337,51 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131733600</t>
+          <t>https://artportalen.se/Sighting/131740536</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128760347</v>
+        <v>131733600</v>
       </c>
       <c r="B26" t="n">
-        <v>87375</v>
+        <v>87371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3739</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699178</v>
+        <v>699155</v>
       </c>
       <c r="R26" t="n">
-        <v>6671333</v>
+        <v>6671396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3404,12 +3408,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3424,24 +3428,28 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760347</t>
+          <t>https://artportalen.se/Sighting/131733600</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129068961</v>
+        <v>128760347</v>
       </c>
       <c r="B27" t="n">
         <v>87375</v>
@@ -3470,19 +3478,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699078</v>
+        <v>699178</v>
       </c>
       <c r="R27" t="n">
-        <v>6671632</v>
+        <v>6671333</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,12 +3514,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3523,35 +3528,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129068961</t>
+          <t>https://artportalen.se/Sighting/128760347</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129068964</v>
+        <v>129068961</v>
       </c>
       <c r="B28" t="n">
         <v>87375</v>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699076</v>
+        <v>699078</v>
       </c>
       <c r="R28" t="n">
-        <v>6671622</v>
+        <v>6671632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3655,51 +3655,54 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129068964</t>
+          <t>https://artportalen.se/Sighting/129068961</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128760345</v>
+        <v>129068964</v>
       </c>
       <c r="B29" t="n">
-        <v>87146</v>
+        <v>87375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3762</v>
+        <v>3739</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699184</v>
+        <v>699076</v>
       </c>
       <c r="R29" t="n">
-        <v>6671328</v>
+        <v>6671622</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3726,12 +3729,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,30 +3743,35 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760345</t>
+          <t>https://artportalen.se/Sighting/129068964</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128760356</v>
+        <v>128760345</v>
       </c>
       <c r="B30" t="n">
         <v>87146</v>
@@ -3798,10 +3806,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699154</v>
+        <v>699184</v>
       </c>
       <c r="R30" t="n">
-        <v>6671383</v>
+        <v>6671328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3859,16 +3867,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760356</t>
+          <t>https://artportalen.se/Sighting/128760345</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131737274</v>
+        <v>128760356</v>
       </c>
       <c r="B31" t="n">
-        <v>87208</v>
+        <v>87146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,14 +3904,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699008</v>
+        <v>699154</v>
       </c>
       <c r="R31" t="n">
-        <v>6671648</v>
+        <v>6671383</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3930,12 +3938,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,28 +3958,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737274</t>
+          <t>https://artportalen.se/Sighting/128760356</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131737275</v>
+        <v>131737274</v>
       </c>
       <c r="B32" t="n">
         <v>87208</v>
@@ -4006,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699030</v>
+        <v>699008</v>
       </c>
       <c r="R32" t="n">
-        <v>6671657</v>
+        <v>6671648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,13 +4075,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737275</t>
+          <t>https://artportalen.se/Sighting/131737274</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131737276</v>
+        <v>131737275</v>
       </c>
       <c r="B33" t="n">
         <v>87208</v>
@@ -4112,10 +4116,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699043</v>
+        <v>699030</v>
       </c>
       <c r="R33" t="n">
-        <v>6671647</v>
+        <v>6671657</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4177,13 +4181,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737276</t>
+          <t>https://artportalen.se/Sighting/131737275</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131737278</v>
+        <v>131737276</v>
       </c>
       <c r="B34" t="n">
         <v>87208</v>
@@ -4214,14 +4218,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699148</v>
+        <v>699043</v>
       </c>
       <c r="R34" t="n">
-        <v>6671394</v>
+        <v>6671647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,13 +4287,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737278</t>
+          <t>https://artportalen.se/Sighting/131737276</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131737280</v>
+        <v>131737278</v>
       </c>
       <c r="B35" t="n">
         <v>87208</v>
@@ -4320,14 +4324,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699034</v>
+        <v>699148</v>
       </c>
       <c r="R35" t="n">
-        <v>6671599</v>
+        <v>6671394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,54 +4393,51 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131737280</t>
+          <t>https://artportalen.se/Sighting/131737278</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129068561</v>
+        <v>131737280</v>
       </c>
       <c r="B36" t="n">
-        <v>93189</v>
+        <v>87208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>698941</v>
+        <v>699034</v>
       </c>
       <c r="R36" t="n">
-        <v>6671657</v>
+        <v>6671599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4477,21 +4478,20 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
@@ -4499,51 +4499,54 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129068561</t>
+          <t>https://artportalen.se/Sighting/131737280</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128760344</v>
+        <v>129068561</v>
       </c>
       <c r="B37" t="n">
-        <v>93193</v>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699192</v>
+        <v>698941</v>
       </c>
       <c r="R37" t="n">
-        <v>6671306</v>
+        <v>6671657</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,12 +4573,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,55 +4587,60 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760344</t>
+          <t>https://artportalen.se/Sighting/129068561</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128760340</v>
+        <v>128760344</v>
       </c>
       <c r="B38" t="n">
-        <v>93209</v>
+        <v>93193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>4363</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4642,10 +4650,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699213</v>
+        <v>699192</v>
       </c>
       <c r="R38" t="n">
-        <v>6671287</v>
+        <v>6671306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4703,16 +4711,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760340</t>
+          <t>https://artportalen.se/Sighting/128760344</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131736814</v>
+        <v>128760340</v>
       </c>
       <c r="B39" t="n">
-        <v>93283</v>
+        <v>93209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4740,14 +4748,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699042</v>
+        <v>699213</v>
       </c>
       <c r="R39" t="n">
-        <v>6671411</v>
+        <v>6671287</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4774,12 +4782,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4794,28 +4802,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131736814</t>
+          <t>https://artportalen.se/Sighting/128760340</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131736815</v>
+        <v>131736814</v>
       </c>
       <c r="B40" t="n">
         <v>93283</v>
@@ -4846,14 +4850,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>698984</v>
+        <v>699042</v>
       </c>
       <c r="R40" t="n">
-        <v>6671480</v>
+        <v>6671411</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4915,13 +4919,13 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131736815</t>
+          <t>https://artportalen.se/Sighting/131736814</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131736816</v>
+        <v>131736815</v>
       </c>
       <c r="B41" t="n">
         <v>93283</v>
@@ -4952,14 +4956,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699008</v>
+        <v>698984</v>
       </c>
       <c r="R41" t="n">
-        <v>6671653</v>
+        <v>6671480</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5021,16 +5025,16 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131736816</t>
+          <t>https://artportalen.se/Sighting/131736815</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130379960</v>
+        <v>131736816</v>
       </c>
       <c r="B42" t="n">
-        <v>93215</v>
+        <v>93283</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5038,46 +5042,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699204</v>
+        <v>699008</v>
       </c>
       <c r="R42" t="n">
-        <v>6671281</v>
+        <v>6671653</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5101,17 +5096,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 ex. under gran.</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5122,74 +5112,82 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Grandominerad barr-/blandskog.</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130379960</t>
+          <t>https://artportalen.se/Sighting/131736816</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128760352</v>
+        <v>130379960</v>
       </c>
       <c r="B43" t="n">
-        <v>92869</v>
+        <v>93215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Vallmar, NNV om Häverö kyrka, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699154</v>
+        <v>699204</v>
       </c>
       <c r="R43" t="n">
-        <v>6671353</v>
+        <v>6671281</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5213,12 +5211,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 ex. under gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5229,31 +5232,36 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grandominerad barr-/blandskog.</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760352</t>
+          <t>https://artportalen.se/Sighting/130379960</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131740321</v>
+        <v>128760352</v>
       </c>
       <c r="B44" t="n">
-        <v>92943</v>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5281,14 +5289,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>698943</v>
+        <v>699154</v>
       </c>
       <c r="R44" t="n">
-        <v>6671660</v>
+        <v>6671353</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5315,12 +5323,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5335,66 +5343,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740321</t>
+          <t>https://artportalen.se/Sighting/128760352</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128760342</v>
+        <v>131740321</v>
       </c>
       <c r="B45" t="n">
-        <v>93223</v>
+        <v>92943</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5448</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699194</v>
+        <v>698943</v>
       </c>
       <c r="R45" t="n">
-        <v>6671305</v>
+        <v>6671660</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5421,12 +5425,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5441,27 +5445,31 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760342</t>
+          <t>https://artportalen.se/Sighting/131740321</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128760346</v>
+        <v>128760342</v>
       </c>
       <c r="B46" t="n">
-        <v>91424</v>
+        <v>93223</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5469,21 +5477,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5733</v>
+        <v>5448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5493,10 +5501,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699179</v>
+        <v>699194</v>
       </c>
       <c r="R46" t="n">
-        <v>6671330</v>
+        <v>6671305</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5554,16 +5562,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760346</t>
+          <t>https://artportalen.se/Sighting/128760342</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131740034</v>
+        <v>128760346</v>
       </c>
       <c r="B47" t="n">
-        <v>91474</v>
+        <v>91424</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5571,34 +5579,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5741</v>
+        <v>5733</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Pinkdal Nordost, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699135</v>
+        <v>699179</v>
       </c>
       <c r="R47" t="n">
-        <v>6671424</v>
+        <v>6671330</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,12 +5633,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,66 +5653,62 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740034</t>
+          <t>https://artportalen.se/Sighting/128760346</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128760341</v>
+        <v>131740034</v>
       </c>
       <c r="B48" t="n">
-        <v>91435</v>
+        <v>91474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Pinkdal Nordost, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699200</v>
+        <v>699135</v>
       </c>
       <c r="R48" t="n">
-        <v>6671298</v>
+        <v>6671424</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,12 +5735,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5751,24 +5755,28 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760341</t>
+          <t>https://artportalen.se/Sighting/131740034</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128760349</v>
+        <v>128760341</v>
       </c>
       <c r="B49" t="n">
         <v>91435</v>
@@ -5803,10 +5811,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699177</v>
+        <v>699200</v>
       </c>
       <c r="R49" t="n">
-        <v>6671345</v>
+        <v>6671298</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5864,38 +5872,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760349</t>
+          <t>https://artportalen.se/Sighting/128760341</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128760339</v>
+        <v>128760349</v>
       </c>
       <c r="B50" t="n">
-        <v>93233</v>
+        <v>91435</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5905,10 +5913,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699211</v>
+        <v>699177</v>
       </c>
       <c r="R50" t="n">
-        <v>6671286</v>
+        <v>6671345</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5966,13 +5974,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760339</t>
+          <t>https://artportalen.se/Sighting/128760349</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128760348</v>
+        <v>128760339</v>
       </c>
       <c r="B51" t="n">
         <v>93233</v>
@@ -6007,10 +6015,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699166</v>
+        <v>699211</v>
       </c>
       <c r="R51" t="n">
-        <v>6671341</v>
+        <v>6671286</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,13 +6076,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760348</t>
+          <t>https://artportalen.se/Sighting/128760339</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128760354</v>
+        <v>128760348</v>
       </c>
       <c r="B52" t="n">
         <v>93233</v>
@@ -6109,10 +6117,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699138</v>
+        <v>699166</v>
       </c>
       <c r="R52" t="n">
-        <v>6671369</v>
+        <v>6671341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6170,56 +6178,51 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760354</t>
+          <t>https://artportalen.se/Sighting/128760348</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129069986</v>
+        <v>128760354</v>
       </c>
       <c r="B53" t="n">
-        <v>44177</v>
+        <v>93233</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>101735</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699009</v>
+        <v>699138</v>
       </c>
       <c r="R53" t="n">
-        <v>6671637</v>
+        <v>6671369</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6246,17 +6249,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,38 +6263,33 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129069986</t>
+          <t>https://artportalen.se/Sighting/128760354</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131735751</v>
+        <v>129069986</v>
       </c>
       <c r="B54" t="n">
-        <v>44182</v>
+        <v>44177</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6322,16 +6315,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vallmar Nordväst, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699038</v>
+        <v>699009</v>
       </c>
       <c r="R54" t="n">
-        <v>6671430</v>
+        <v>6671637</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6368,7 +6366,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Spår i fnösketicka. Björkhögstubbe.</t>
+          <t>Spår i fnösketicka på björkhögstubbe. Igenväxt tidigare jordbruksmark.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6377,13 +6375,14 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -6398,51 +6397,51 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131735751</t>
+          <t>https://artportalen.se/Sighting/129069986</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131740317</v>
+        <v>131735751</v>
       </c>
       <c r="B55" t="n">
-        <v>111471</v>
+        <v>44182</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219711</v>
+        <v>101735</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Vallmar Nordväst, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>698952</v>
+        <v>699038</v>
       </c>
       <c r="R55" t="n">
-        <v>6671645</v>
+        <v>6671430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6477,6 +6476,11 @@
           <t>2025-10-10</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Spår i fnösketicka. Björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6504,54 +6508,54 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740317</t>
+          <t>https://artportalen.se/Sighting/131735751</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>105310328</v>
+        <v>131740317</v>
       </c>
       <c r="B56" t="n">
-        <v>99096</v>
+        <v>111471</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699290</v>
+        <v>698952</v>
       </c>
       <c r="R56" t="n">
-        <v>6671272</v>
+        <v>6671645</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6575,12 +6579,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,16 +6595,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>3 plantor</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6613,19 +6607,23 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310328</t>
+          <t>https://artportalen.se/Sighting/131740317</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128760357</v>
+        <v>105310328</v>
       </c>
       <c r="B57" t="n">
-        <v>99153</v>
+        <v>99096</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6633,21 +6631,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219874</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6657,13 +6655,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699153</v>
+        <v>699290</v>
       </c>
       <c r="R57" t="n">
-        <v>6671384</v>
+        <v>6671272</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6687,12 +6685,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6703,28 +6701,38 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>3 plantor</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760357</t>
+          <t>https://artportalen.se/Sighting/105310328</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128760359</v>
+        <v>128760357</v>
       </c>
       <c r="B58" t="n">
         <v>99153</v>
@@ -6759,10 +6767,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699100</v>
+        <v>699153</v>
       </c>
       <c r="R58" t="n">
-        <v>6671402</v>
+        <v>6671384</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6820,38 +6828,38 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760359</t>
+          <t>https://artportalen.se/Sighting/128760357</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128760358</v>
+        <v>128760359</v>
       </c>
       <c r="B59" t="n">
-        <v>102240</v>
+        <v>99153</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6861,10 +6869,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699099</v>
+        <v>699100</v>
       </c>
       <c r="R59" t="n">
-        <v>6671403</v>
+        <v>6671402</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6922,16 +6930,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760358</t>
+          <t>https://artportalen.se/Sighting/128760359</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131740600</v>
+        <v>128760358</v>
       </c>
       <c r="B60" t="n">
-        <v>102318</v>
+        <v>102240</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6959,14 +6967,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bolviken Sydost, Upl</t>
+          <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>698989</v>
+        <v>699099</v>
       </c>
       <c r="R60" t="n">
-        <v>6671491</v>
+        <v>6671403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6993,12 +7001,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7013,28 +7021,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740600</t>
+          <t>https://artportalen.se/Sighting/128760358</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131740601</v>
+        <v>131740600</v>
       </c>
       <c r="B61" t="n">
         <v>102318</v>
@@ -7065,14 +7069,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bolviken Syd, Upl</t>
+          <t>Bolviken Sydost, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>698950</v>
+        <v>698989</v>
       </c>
       <c r="R61" t="n">
-        <v>6671639</v>
+        <v>6671491</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7134,54 +7138,54 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740601</t>
+          <t>https://artportalen.se/Sighting/131740600</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>105310331</v>
+        <v>131740601</v>
       </c>
       <c r="B62" t="n">
-        <v>101326</v>
+        <v>102318</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vallmar, Upl</t>
+          <t>Bolviken Syd, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>699257</v>
+        <v>698950</v>
       </c>
       <c r="R62" t="n">
-        <v>6671312</v>
+        <v>6671639</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7205,12 +7209,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7221,11 +7225,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7238,19 +7237,23 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310331</t>
+          <t>https://artportalen.se/Sighting/131740601</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128760353</v>
+        <v>105310331</v>
       </c>
       <c r="B63" t="n">
-        <v>101227</v>
+        <v>101326</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7258,21 +7261,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7282,13 +7285,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>699156</v>
+        <v>699257</v>
       </c>
       <c r="R63" t="n">
-        <v>6671355</v>
+        <v>6671312</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7312,12 +7315,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7328,69 +7331,71 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760353</t>
+          <t>https://artportalen.se/Sighting/105310331</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128934451</v>
+        <v>128760353</v>
       </c>
       <c r="B64" t="n">
-        <v>92688</v>
+        <v>101227</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>232138</v>
+        <v>222771</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>698916</v>
+        <v>699156</v>
       </c>
       <c r="R64" t="n">
-        <v>6671640</v>
+        <v>6671355</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7417,17 +7422,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Även fläckfingersvamp i direkt närhet.</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7436,35 +7436,30 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128934451</t>
+          <t>https://artportalen.se/Sighting/128760353</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129070080</v>
+        <v>128934451</v>
       </c>
       <c r="B65" t="n">
         <v>92688</v>
@@ -7502,10 +7497,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>698918</v>
+        <v>698916</v>
       </c>
       <c r="R65" t="n">
-        <v>6671642</v>
+        <v>6671640</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7532,12 +7527,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Även fläckfingersvamp i direkt närhet.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,13 +7568,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129070080</t>
+          <t>https://artportalen.se/Sighting/128934451</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129070090</v>
+        <v>129070080</v>
       </c>
       <c r="B66" t="n">
         <v>92688</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>698978</v>
+        <v>698918</v>
       </c>
       <c r="R66" t="n">
         <v>6671642</v>
@@ -7678,13 +7678,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129070090</t>
+          <t>https://artportalen.se/Sighting/129070080</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129070093</v>
+        <v>129070090</v>
       </c>
       <c r="B67" t="n">
         <v>92688</v>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>699021</v>
+        <v>698978</v>
       </c>
       <c r="R67" t="n">
         <v>6671642</v>
@@ -7788,38 +7788,38 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129070093</t>
+          <t>https://artportalen.se/Sighting/129070090</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129070230</v>
+        <v>129070093</v>
       </c>
       <c r="B68" t="n">
-        <v>87323</v>
+        <v>92688</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>249228</v>
+        <v>232138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>699079</v>
+        <v>699021</v>
       </c>
       <c r="R68" t="n">
-        <v>6671615</v>
+        <v>6671642</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,16 +7898,16 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129070230</t>
+          <t>https://artportalen.se/Sighting/129070093</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128760355</v>
+        <v>129070230</v>
       </c>
       <c r="B69" t="n">
-        <v>87346</v>
+        <v>87323</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7915,34 +7915,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6003295</v>
+        <v>249228</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>699151</v>
+        <v>699079</v>
       </c>
       <c r="R69" t="n">
-        <v>6671385</v>
+        <v>6671615</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7969,12 +7972,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7990,24 +7993,28 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760355</t>
+          <t>https://artportalen.se/Sighting/129070230</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129068748</v>
+        <v>128760355</v>
       </c>
       <c r="B70" t="n">
         <v>87346</v>
@@ -8036,19 +8043,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>698990</v>
+        <v>699151</v>
       </c>
       <c r="R70" t="n">
-        <v>6671640</v>
+        <v>6671385</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8075,12 +8079,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8096,28 +8100,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129068748</t>
+          <t>https://artportalen.se/Sighting/128760355</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129068763</v>
+        <v>129068748</v>
       </c>
       <c r="B71" t="n">
         <v>87346</v>
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>699044</v>
+        <v>698990</v>
       </c>
       <c r="R71" t="n">
-        <v>6671648</v>
+        <v>6671640</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8221,13 +8221,13 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129068763</t>
+          <t>https://artportalen.se/Sighting/129068748</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129068822</v>
+        <v>129068763</v>
       </c>
       <c r="B72" t="n">
         <v>87346</v>
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>699119</v>
+        <v>699044</v>
       </c>
       <c r="R72" t="n">
-        <v>6671545</v>
+        <v>6671648</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8331,16 +8331,16 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129068822</t>
+          <t>https://artportalen.se/Sighting/129068763</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128883852</v>
+        <v>129068822</v>
       </c>
       <c r="B73" t="n">
-        <v>92328</v>
+        <v>87346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8348,34 +8348,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6040162</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>699201</v>
+        <v>699119</v>
       </c>
       <c r="R73" t="n">
-        <v>6671236</v>
+        <v>6671545</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8402,12 +8405,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8416,66 +8419,73 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128883852</t>
+          <t>https://artportalen.se/Sighting/129068822</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129069258</v>
+        <v>128883852</v>
       </c>
       <c r="B74" t="n">
-        <v>93224</v>
+        <v>92328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6331651</v>
+        <v>6040162</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon melilotinus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Quél.) Svantesson</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vallmar, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>699009</v>
+        <v>699201</v>
       </c>
       <c r="R74" t="n">
-        <v>6671637</v>
+        <v>6671236</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8502,12 +8512,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8516,60 +8526,50 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129069258</t>
+          <t>https://artportalen.se/Sighting/128883852</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129070007</v>
+        <v>129069258</v>
       </c>
       <c r="B75" t="n">
-        <v>93225</v>
+        <v>93224</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6332770</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
+        <v>6331651</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon melilotinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Quél.) Svantesson</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>699032</v>
+        <v>699009</v>
       </c>
       <c r="R75" t="n">
-        <v>6671609</v>
+        <v>6671637</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8647,6 +8647,116 @@
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129069258</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129070007</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vallmar, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>699032</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6671609</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129070007</t>
         </is>
@@ -8728,6 +8838,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91573</v>
+        <v>91575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91575</v>
+        <v>91577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91577</v>
+        <v>91578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91578</v>
+        <v>91579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91579</v>
+        <v>91580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91587</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>91600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91600</v>
+        <v>91601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91601</v>
+        <v>91614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
